--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -153,12 +141,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,7 +754,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="3" t="n">
         <v>31.7</v>
       </c>
       <c r="E4" s="3" t="n">
@@ -792,45 +774,47 @@
       </c>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.6</v>
+        <v>23.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>76.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -846,21 +830,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="9" t="n">
-        <v>26.2</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>31.7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>24.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -872,38 +862,44 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>262</v>
+        <v>14.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O5" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>92.7</v>
+        <v>2</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S5" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>7.2</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>14.4</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X5" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y5" s="3" t="n">
         <v>6.8</v>
       </c>
@@ -921,70 +917,69 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>32.2</v>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
+        <v>81.2</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>61.5</v>
+      </c>
       <c r="V6" s="3" t="n">
-        <v>23.9</v>
+        <v>5.1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>74.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>4.2</v>
@@ -1003,70 +998,76 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="9" t="n">
-        <v>30.5</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>25.2</v>
+        <v>7</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>4.6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O7" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>19.5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="inlineStr">
@@ -1083,67 +1084,71 @@
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="9" t="n">
-        <v>26.8</v>
+      <c r="D8" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>18.4</v>
+        <v>12.9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.6</v>
+        <v>25.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.4</v>
+        <v>15.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>18.9</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>25.8</v>
+        <v>20.1</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>66.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>5.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>59.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1161,68 +1166,66 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="9" t="n">
-        <v>147.4</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="F9" s="11" t="n"/>
+        <v>26.8</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>8.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>57.8</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>18.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>11.4</v>
+        <v>2.1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>94.2</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n">
-        <v>318.6</v>
+        <v>2.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.8</v>
+        <v>4.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.6</v>
+        <v>1.4</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>110.8</v>
+        <v>2.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>23.6</v>
+        <v>2.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>382.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1239,67 +1242,69 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>23.7</v>
+      <c r="D10" s="9" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>16.2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>591.2</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>52.1</v>
+      </c>
       <c r="P10" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>19.1</v>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n">
-        <v>24.5</v>
+        <v>6.3</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>23.8</v>
+        <v>48.8</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>26.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>16.2</v>
+        <v>38.6</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>31.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
@@ -1316,67 +1321,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>23.8</v>
+      <c r="D11" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>43.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>81</v>
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M11" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>2.1</v>
+        <v>94.2</v>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.4</v>
+        <v>2</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>24.8</v>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.2</v>
+        <v>2.2</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1393,67 +1400,75 @@
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>18.5</v>
+      <c r="D12" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+577
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N12" s="3" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>29.6</v>
+      </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>0.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>934.8</v>
+        <v>8.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>25.1</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>0.1</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>24.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22.9</v>
+        <v>4.8</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>26.8</v>
+        <v>25.4</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>81.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
@@ -1471,66 +1486,70 @@
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O13" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="P13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>24.3</v>
+        <v>93.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>62.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="U13" s="3" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V13" s="3" t="n">
-        <v>21.8</v>
+        <v>2.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.4</v>
+        <v>46.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1548,70 +1567,68 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>16.5</v>
+        <v>26.4</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>6.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.2</v>
+        <v>2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.4</v>
+        <v>25.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>2.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>25.2</v>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>83.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="inlineStr">
@@ -1629,66 +1646,70 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>29.9</v>
+        <v>26.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>22.5</v>
+        <v>18.5</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16.5</v>
+        <v>98.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
+        <v>18.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>46.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>22.8</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26.4</v>
+        <v>12.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>17.2</v>
+        <v>85.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>51.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
@@ -1705,69 +1726,67 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="10" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>116.6</v>
+      <c r="D16" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>13.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>92.3</v>
+        <v>1.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>951.3</v>
+        <v>19.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>953.2</v>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>5.3</v>
+        <v>92.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>26.6</v>
+        <v>12.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>18.2</v>
+        <v>5.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1841.7</v>
+        <v>2.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>20.9</v>
+        <v>2.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>24.4</v>
+        <v>26.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1784,65 +1803,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>81.09999999999999</v>
+      <c r="D17" s="9" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>42.9</v>
+      </c>
       <c r="R17" s="8" t="n">
-        <v>26.6</v>
+        <v>46.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>26.6</v>
+        <v>5.7</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>704.3</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>85.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>151</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1859,67 +1884,71 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
-        <v>25.1</v>
+      <c r="D18" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
+        <v>48.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n">
-        <v>21.5</v>
+        <v>4.1</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.8</v>
+        <v>14.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>82.2</v>
+        <v>48.3</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
@@ -1936,69 +1965,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="12" t="n">
-        <v>3</v>
+      <c r="D19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>6262.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n">
-        <v>981.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.8</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>254.3</v>
+        <v>4.8</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>85.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2016,68 +2047,70 @@
       </c>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>17.6</v>
+        <v>46.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>28.3</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n"/>
+        <v>85.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>19.9</v>
+        <v>32.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>19.8</v>
+        <v>2</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.2</v>
+        <v>4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>20.2</v>
+        <v>2.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>1.9</v>
+        <v>258.3</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2095,68 +2128,70 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.5</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>39.2</v>
+        <v>12.6</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>9.6</v>
+        <v>2.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>12.6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>292.2</v>
+        <v>393.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92.2</v>
+        <v>927.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>12.8</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.9</v>
+        <v>18.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
+        <v>20.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>29.2</v>
+      </c>
       <c r="V21" s="3" t="n">
-        <v>19.9</v>
+        <v>2.2</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>90.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2174,70 +2209,70 @@
       </c>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
+        <v>38.1</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13.9</v>
+        <v>8.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="K22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+        <v>2.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>29.9</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>26.2</v>
+        <v>42.8</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>80.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2254,71 +2289,71 @@
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>119.2</v>
+      <c r="D23" s="9" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.9</v>
+        <v>1.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>68.8</v>
+        <v>15.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>389.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>96.2</v>
+        <v>3.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>185.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>1393.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.4</v>
+        <v>26</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.9</v>
+        <v>41.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>119.9</v>
+        <v>1.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>536</v>
+        <v>25.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>37.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>12.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>22.9</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>427.8</v>
+        <v>230.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2335,66 +2370,68 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="D24" s="9" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n">
-        <v>98.8</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>19.2</v>
+        <v>1.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>391.2</v>
+        <v>20</v>
       </c>
       <c r="P24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>85.2</v>
+        <v>80.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
@@ -2414,71 +2451,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="12" t="n">
-        <v>0.2</v>
+      <c r="D25" s="10" t="n">
+        <v>44.6</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>24.9</v>
+        <v>9.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.1</v>
+        <v>5.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="I25" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>0.8</v>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 1
+</t>
+        </is>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2495,69 +2535,71 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n">
-        <v>28.6</v>
+      <c r="D26" s="10" t="n">
+        <v>29.51</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>23.9</v>
+        <v>8.1</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="K26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>80.2</v>
+        <v>8.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2575,68 +2617,70 @@
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n">
-        <v>23.3</v>
+        <v>29.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>22.4</v>
+        <v>18.7</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>4.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>1.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>12.9</v>
       </c>
       <c r="I27" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>10</v>
+        <v>93.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>39.3</v>
+        <v>25.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>34.9</v>
+        <v>6.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22</v>
+        <v>2.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>28.2</v>
+        <v>24.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>53.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2653,71 +2697,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n">
-        <v>32.7</v>
+      <c r="D28" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>24.3</v>
+        <v>17.4</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>958.4</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>92.2</v>
+        <v>29.1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>21.2</v>
+        <v>2.1</v>
       </c>
       <c r="S28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>853.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Y28" s="3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>2.3</v>
       </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2735,70 +2779,70 @@
       </c>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F29" s="9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.7</v>
+        <v>16.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>35.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.2</v>
+        <v>16.8</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>651.1</v>
+        <v>682.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>90.2</v>
+        <v>92.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>451.6</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>26.4</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>2.2</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2815,71 +2859,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="10" t="n">
-        <v>149.4</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>1.3</v>
+      <c r="D30" s="9" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>92.8</v>
+        <v>18.5</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4.5</v>
+        <v>3908.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>91.2</v>
+        <v>2.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.1</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>26.9</v>
+        <v>12.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>922.2</v>
+        <v>322.2</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>44.2</v>
+        <v>49.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>82.8</v>
+        <v>134.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>20.8</v>
+        <v>1042.6</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>22.9</v>
+        <v>14.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>17.2</v>
+        <v>322.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6.5</v>
+        <v>24.4</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2896,69 +2940,71 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="10" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>13.9</v>
+      <c r="D31" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>89.59999999999999</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>23.9</v>
+        <v>3.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19.8</v>
+        <v>58.2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>18.5</v>
+      <c r="M31" s="8" t="n">
+        <v>751.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>452.6</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2644.4</v>
+        <v>28.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>15.5</v>
+        <v>48.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>3</v>
+        <v>63.5</v>
       </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2975,67 +3021,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="12" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
+      <c r="D32" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.5</v>
+        <v>0.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>28.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>26.8</v>
+        <v>2.6</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.3</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>23</v>
+        <v>2.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>27.4</v>
+        <v>0.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>80.3</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3052,69 +3102,71 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="12" t="n">
-        <v>393.26</v>
-      </c>
-      <c r="E33" s="3" t="n">
+      <c r="D33" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>19.8</v>
+        <v>5.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>81.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="O33" s="3" t="n"/>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>22.9</v>
+        <v>2.3</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>4.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.5</v>
+        <v>24.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>86.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3130,43 +3182,51 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="n">
-        <v>32.1</v>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>3.6</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>25.8</v>
+        <v>5.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12.7</v>
+        <v>14.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="8" t="n">
-        <v>81.2</v>
+        <v>0.9</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>78.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>928.2</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3175,25 +3235,25 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>24.2</v>
+        <v>2.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>62.8</v>
+        <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3210,69 +3270,67 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="D35" s="10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="G35" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>18.2</v>
-      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="N35" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>928.2</v>
-      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.8</v>
+        <v>45.1</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.9</v>
+        <v>4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>22.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3288,68 +3346,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>23.6</v>
+        <v>30.4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>25.8</v>
+        <v>18.4</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>2.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>454.2</v>
+        <v>18.2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>2.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>8090.2</v>
-      </c>
-      <c r="O36" s="3" t="n"/>
+      <c r="N36" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U36" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="V36" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>37.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3366,69 +3432,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>392.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>126.9</v>
+      <c r="D37" s="9" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>25.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>84634.39999999999</v>
+        <v>4.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>1.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1441.8</v>
+        <v>0.3</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>7.5</v>
+        <v>12.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>26.9</v>
+        <v>48.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>10.3</v>
+        <v>90.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.9</v>
+        <v>1242.1</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>22.2</v>
+        <v>1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>25.2</v>
+        <v>125.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>13.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>4.3</v>
+        <v>32.4</v>
       </c>
       <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3445,38 +3513,36 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="10" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>25.4</v>
+      <c r="D38" s="9" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>26.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>13.9</v>
+        <v>9.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17.4</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>8338.4</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>81.8</v>
+        <v>9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.2</v>
@@ -3485,31 +3551,31 @@
         <v>2.6</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>11.6</v>
+        <v>25.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>23.5</v>
+        <v>2.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>17.9</v>
+        <v>14.1</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>24.8</v>
+        <v>48.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3526,67 +3592,69 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n">
-        <v>32.8</v>
+      <c r="D39" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>51.6</v>
+        <v>18.9</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>54.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.3</v>
+        <v>32.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="N39" s="3" t="n">
-        <v>19.8</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>28.6</v>
+        <v>18.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.2</v>
+        <v>6.2</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>72.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>194.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3602,70 +3670,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="12" t="n">
-        <v>92.5</v>
+      <c r="C40" s="3" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>32.6</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>85.40000000000001</v>
+        <v>13.5</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>98.3</v>
+        <v>17</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>27.8</v>
+        <v>18.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>27.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.6</v>
+        <v>2.9</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.9</v>
+        <v>2.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z40" s="3" t="n"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -3681,65 +3751,71 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>42.2</v>
+      </c>
       <c r="D41" s="3" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>14.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>18.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="N41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O41" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>31.2</v>
+        <v>3.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3758,69 +3834,69 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>72.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>21</v>
+        <v>2.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3.6</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1.8</v>
+        <v>89</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>922.1</v>
+      <c r="N42" s="3" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>14.8</v>
+        <v>4.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="T42" s="3" t="n"/>
+      <c r="T42" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
+        <v>24.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>2.6</v>
@@ -3839,26 +3915,24 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>12.5</v>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3.6</v>
@@ -3866,37 +3940,57 @@
       <c r="K43" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="L43" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+6
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>381.9</v>
+        <v>6.8</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>95.3</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>95.7</v>
+        <v>85.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>27.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.2</v>
+        <v>24.3</v>
       </c>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3913,63 +4007,78 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>2</v>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4262
+7
+</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>44.2</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>54.7</v>
+        <v>5.4</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+14
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+7
+</t>
+        </is>
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>366.3</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="8" t="n">
-        <v>6.9</v>
+      <c r="P44" s="3" t="n">
+        <v>106.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>121.3</v>
+        <v>41.8</v>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.8</v>
+        <v>2.4</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.2</v>
+      <c r="X44" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>5.4</v>
+        <v>50.4</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -3986,29 +4095,29 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E45" s="10" t="n">
+      <c r="D45" s="9" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>25.5</v>
+      <c r="F45" s="9" t="n">
+        <v>192.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.5</v>
+        <v>282.8</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18.4</v>
@@ -4016,19 +4125,25 @@
       <c r="M45" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n">
-        <v>98.3</v>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>25.7</v>
+        <v>5.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>60.2</v>
+        <v>6.2</v>
       </c>
       <c r="T45" s="3" t="n"/>
       <c r="U45" s="3" t="n">
@@ -4036,11 +4151,8 @@
       </c>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
+      <c r="X45" s="3" t="n">
+        <v>83.2</v>
       </c>
       <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
@@ -4057,60 +4169,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="10" t="n">
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E46" s="10" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>0.1</v>
+      <c r="E46" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="n">
+        <v>290.1</v>
+      </c>
       <c r="V46" s="8" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>150.1</v>
-      </c>
+      <c r="W46" s="3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -141,6 +159,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -753,15 +780,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n">
-        <v>31.7</v>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="9" t="n">
+        <v>91.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>24.3</v>
+      <c r="F4" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
@@ -772,51 +799,49 @@
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
-        <v>8.9</v>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>851.8</v>
-      </c>
       <c r="S4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" s="3" t="n"/>
+        <v>29.3</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>545.2</v>
+      </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W4" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -830,27 +855,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>16.9</v>
+        <v>26.2</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>14.8</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15.3</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -862,48 +881,50 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>18.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>13.8</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>7.2</v>
+        <v>21</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>14.4</v>
+        <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>18.6</v>
+        <v>6.5</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -917,74 +938,72 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>17.4</v>
+        <v>34.2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21.8</v>
+        <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>7.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>61.5</v>
+        <v>207.4</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>51.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>86.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+        <v>77.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -998,78 +1017,70 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.2</v>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>4.6</v>
+        <v>19.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15.2</v>
+        <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>31.6</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" s="3" t="n"/>
+        <v>20.1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>26.8</v>
+        <v>22.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>14.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>41.3</v>
+        <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>4.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="3" t="n"/>
+        <v>86.2</v>
+      </c>
+      <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1083,74 +1094,72 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>12.9</v>
+        <v>26.8</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>25.2</v>
+        <v>22.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.4</v>
+        <v>18.9</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>22.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>3.5</v>
+        <v>25.8</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>5.2</v>
+        <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.2</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>19.8</v>
+        <v>8.4</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>86.2</v>
+        <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+        <v>7.3</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1164,70 +1173,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>4.1</v>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="10" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>112.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8.4</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.3</v>
+        <v>957.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2.1</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.9</v>
+        <v>949.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>20.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O9" s="3" t="n"/>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>1454.6</v>
+      </c>
       <c r="P9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R9" s="3" t="n"/>
+        <v>129.4</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1110.9</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>2.2</v>
+        <v>142.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>4.2</v>
+        <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.4</v>
+        <v>1948.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>2.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+        <v>231.1</v>
+      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1241,72 +1250,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="9" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>5.8</v>
-      </c>
+        <v>11.6</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>97.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>52.1</v>
+        <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
+        <v>25.9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="S10" s="3" t="n">
-        <v>6.3</v>
+        <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>48.8</v>
+        <v>164.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>38.6</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>216.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1320,72 +1327,70 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>43.7</v>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>2</v>
+        <v>23.8</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>18.8</v>
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>23.8</v>
+        <v>161.2</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>6.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>181.2</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1399,78 +1404,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>1.9</v>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>23.8</v>
+        <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11.6</v>
+        <v>8.9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>29.6</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="n">
-        <v>0.1</v>
+        <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>8.4</v>
+        <v>24.9</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>28.5</v>
-      </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>161.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>24.8</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>4.8</v>
+        <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>194.5</v>
+      </c>
+      <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1484,74 +1481,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
-        <v>29</v>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="11" t="n">
+        <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>2.4</v>
+        <v>12.5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>93.8</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>62.7</v>
+        <v>46.4</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>43</v>
+        <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>81.2</v>
+        <v>20</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>185.2</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1565,72 +1556,72 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="11" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>923.4</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>51.4</v>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1644,74 +1635,70 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n">
-        <v>26.8</v>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="11" t="n">
+        <v>28.9</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>2.2</v>
+        <v>18.6</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>2.7</v>
+        <v>16.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>91</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>12.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>46.6</v>
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>15.2</v>
+        <v>38.2</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2</v>
+        <v>21.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.8</v>
+        <v>85.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+        <v>10.3</v>
+      </c>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1725,70 +1712,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="9" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>2.5</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="11" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.5</v>
+        <v>0.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>13.9</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>92.2</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>32.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>42.9</v>
+        <v>1182.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>5.2</v>
+        <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>118.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>2.2</v>
+        <v>1949.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>26.8</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>4.2</v>
+        <v>1708.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+        <v>1151</v>
+      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1802,74 +1791,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="9" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>16.6</v>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Y17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1883,74 +1864,70 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="10" t="n">
-        <v>1.8</v>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>2.3</v>
+        <v>13.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.1</v>
+        <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.2</v>
+        <v>46.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>95.3</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>91.2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>12.3</v>
-      </c>
+        <v>228.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.4</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>12.4</v>
+        <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>492.1</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>48.3</v>
+        <v>85.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1964,74 +1941,66 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="9" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>23.7</v>
-      </c>
       <c r="G19" s="3" t="n">
-        <v>9.6</v>
+        <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.6</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>6262.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>34.3</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="n">
-        <v>26.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>2</v>
+        <v>19.9</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>6.5</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>2.5</v>
+        <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>28.2</v>
+        <v>21.8</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2045,74 +2014,68 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>30.9</v>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>13.8</v>
+        <v>18.9</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.2</v>
+        <v>19.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46.8</v>
+        <v>48.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32.4</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>5.2</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>2.8</v>
+      <c r="V20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>258.3</v>
+        <v>22.1</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>9.6</v>
+      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2126,74 +2089,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>30.5</v>
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>12.6</v>
+        <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.9</v>
+        <v>23.2</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>1.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.6</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>393.2</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>927.2</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="n">
-        <v>26.2</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>20.2</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.2</v>
+        <v>10.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>2.2</v>
+        <v>19.1</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+        <v>10.8</v>
+      </c>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2207,74 +2166,72 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>38.1</v>
+        <v>29.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>8.9</v>
+        <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>39.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>18.4</v>
+        <v>956.2</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>39.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42.8</v>
+        <v>22.6</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>15.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>194.7</v>
+      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2288,74 +2245,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="9" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="10" t="n">
+        <v>1144.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>389.4</v>
+        <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.8</v>
+        <v>2464.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>185.1</v>
+        <v>7.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1393.2</v>
-      </c>
+        <v>1420.9</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>26</v>
+        <v>931.6</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>41.2</v>
+        <v>1121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.3</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>25.2</v>
+        <v>4.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9360.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.3</v>
+        <v>1108.4</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>12.2</v>
+        <v>102.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>22.9</v>
+        <v>197.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>230.2</v>
+        <v>927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2369,74 +2320,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="9" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>3.9</v>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>829.8</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>282.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>8.5</v>
+        <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>360.5</v>
+        <v>27.6</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.2</v>
+        <v>728.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.4</v>
+        <v>6.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4.6</v>
+        <v>20.5</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.2</v>
+        <v>22.5</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>80.2</v>
+        <v>85.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2450,77 +2393,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="10" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>183.2</v>
-      </c>
       <c r="K25" s="3" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>97.8</v>
-      </c>
+        <v>15.2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>22.1</v>
+        <v>1192.2</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2.8</v>
+        <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>34.2</v>
+        <v>11.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>16.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 1
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>23.2</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2534,74 +2472,70 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="10" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>2.8</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>53.2</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>26.2</v>
+        <v>91.5</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>4.6</v>
+        <v>27.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>6.8</v>
+        <v>716.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>24.2</v>
+        <v>5.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>8.5</v>
+        <v>24.5</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2615,74 +2549,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>4.3</v>
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.1</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>93.8</v>
+        <v>49.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.3</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>6.2</v>
+        <v>24</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+        <v>5.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2696,74 +2626,72 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>15.8</v>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>19.2</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>18</v>
+        <v>46.3</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>68.7</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>0.2</v>
+        <v>119080.9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.6</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.1</v>
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>25.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>853.9</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2.9</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>2.2</v>
+        <v>21</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>62.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2777,74 +2705,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F29" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16.8</v>
+        <v>11.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>91.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>89.2</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>682.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>92.8</v>
-      </c>
+        <v>95.8</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>6.4</v>
+      <c r="S29" s="8" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>12.4</v>
+        <v>20.8</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>39.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2858,74 +2784,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="9" t="n">
-        <v>306.1</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>4.3</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="10" t="n">
+        <v>19498.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.2</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.5</v>
+        <v>292.7</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>3908.6</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>2.4</v>
+        <v>41.2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.7</v>
+        <v>120.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>322.2</v>
-      </c>
+        <v>1112.3</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>49.2</v>
+        <v>153822.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>134.6</v>
+        <v>16.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1042.6</v>
+        <v>1104.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>14.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>322.5</v>
+        <v>312.6</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>928.4</v>
+      </c>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2939,74 +2861,68 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>3.1</v>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>58.2</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>751.1</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>19.4</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>452.6</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>39.7</v>
+        <v>91.2</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R31" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T31" s="3" t="n">
-        <v>48.2</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>2.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.3</v>
+        <v>17.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3020,74 +2936,70 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.8</v>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I32" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1219.6</v>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="Q32" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>2.6</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0.9</v>
+        <v>25.3</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>84.5</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3101,42 +3013,38 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>48.41</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>0.8</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.5</v>
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>5.6</v>
+        <v>94.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>1.2</v>
+        <v>90.2</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3145,30 +3053,30 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>2.3</v>
+        <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>15</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>28.2</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.4</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>168.8</v>
+      </c>
+      <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3182,51 +3090,39 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>3.6</v>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="11" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>5.3</v>
+        <v>19.4</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>41.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
+        <v>93.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.9</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="8" t="n">
+        <v>282.5</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3235,27 +3131,27 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>29.6</v>
+        <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>63.2</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X34" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X34" s="8" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+        <v>16.9</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3269,70 +3165,70 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>2.4</v>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>25.8</v>
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" s="3" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>6.8</v>
+        <v>24.2</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3346,78 +3242,70 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>30.4</v>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="11" t="n">
+        <v>23.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>2.9</v>
+        <v>19</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>18.2</v>
+        <v>15.6</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>51.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.9</v>
+        <v>91.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>31.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>231.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>97.3</v>
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U36" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.9</v>
+        <v>23.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>58.2</v>
+        <v>27</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3431,74 +3319,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="9" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>25.8</v>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="10" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.5</v>
+        <v>8711</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.3</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.5</v>
+        <v>42.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.7</v>
+        <v>981.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>9450.299999999999</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>90.2</v>
+        <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>12.2</v>
-      </c>
       <c r="R37" s="3" t="n">
-        <v>2.4</v>
+        <v>111</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>48.8</v>
+        <v>241.3</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>90.3</v>
+        <v>100.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1242.1</v>
+        <v>124.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>125.2</v>
+        <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>267.2</v>
+        <v>367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3512,72 +3398,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="9" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>26.3</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="11" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>51.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>9.4</v>
+        <v>19.9</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>81</v>
+        <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.1</v>
+        <v>21.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>90.2</v>
+        <v>41</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
+        <v>91.2</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>25.8</v>
+        <v>28.6</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>2.6</v>
+        <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>85.2</v>
+        <v>14.2</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z38" s="3" t="n"/>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3591,72 +3475,72 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="10" t="n">
-        <v>2.3</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="8" t="n">
+        <v>32.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>245.16</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
+        <v>61.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="M39" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>18.6</v>
+        <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6.2</v>
+        <v>1948.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
+        <v>82</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+        <v>114.4</v>
+      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3670,74 +3554,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>13.5</v>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>89</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L40" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O40" s="3" t="n"/>
+        <v>42.1</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="n">
+        <v>92.3</v>
+      </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>18.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>47.8</v>
+        <v>39.8</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.9</v>
+        <v>25.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>7.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z40" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3751,76 +3633,72 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>32.5</v>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="8" t="n">
+        <v>32.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>25.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>85.59999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>28.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18.9</v>
+        <v>15.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>0.1</v>
+        <v>92.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>2.8</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.6</v>
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3834,74 +3712,70 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n">
-        <v>31.8</v>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="9" t="n">
+        <v>12.29</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>25.4</v>
+        <v>24.6</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>10.2</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>7</v>
+        <v>54.4</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>0.1</v>
+        <v>266.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.6</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>49.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>72</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>24.8</v>
+        <v>96.3</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>60.3</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>82.2</v>
+        <v>271.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>216.7</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3915,84 +3789,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4006,81 +3826,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4094,68 +3863,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="9" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="10" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>18.7</v>
       </c>
-      <c r="F45" s="9" t="n">
-        <v>192.9</v>
+      <c r="F45" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>69.8</v>
+        <v>117.5</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>190.9</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>5.7</v>
+        <v>22.9</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T45" s="3" t="n"/>
+        <v>160.5</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+        <v>22.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>24.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4169,67 +3938,38 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>290.1</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>9885.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>116560.8</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,20 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -162,12 +150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,48 +769,50 @@
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>24.2</v>
+      <c r="F4" s="9" t="n">
+        <v>84.5</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="J4" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12.4</v>
+        <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.6</v>
+        <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>29.3</v>
+        <v>2.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>545.2</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
@@ -857,22 +841,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>11.4</v>
+        <v>25.2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.8</v>
@@ -881,46 +865,46 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>17.6</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>29.8</v>
+        <v>20.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X5" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>76.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -940,39 +924,43 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E6" s="8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="J6" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O6" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -984,16 +972,16 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>51.3</v>
+        <v>2.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
@@ -1002,7 +990,7 @@
         <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1018,20 +1006,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="8" t="n">
-        <v>10.5</v>
+      <c r="D7" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>25.2</v>
+      <c r="F7" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>17.8</v>
+      <c r="H7" s="8" t="n">
+        <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1042,16 +1030,18 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20.1</v>
@@ -1060,14 +1050,12 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>81.2</v>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
@@ -1075,12 +1063,14 @@
         <v>20.6</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="n">
+        <v>114.8</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1098,11 +1088,11 @@
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>22.6</v>
+      <c r="F8" s="9" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1111,13 +1101,13 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>18.9</v>
@@ -1127,15 +1117,15 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1147,8 +1137,8 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>94.59999999999999</v>
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1157,9 +1147,11 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1178,25 +1170,25 @@
         <v>147.4</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>89.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>112.5</v>
+        <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>51.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>957.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>949.2</v>
+        <v>47.1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1204,9 +1196,11 @@
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>100.1</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1454.6</v>
+        <v>451.6</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1215,26 +1209,28 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1110.9</v>
+        <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>142.5</v>
+        <v>126</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>123.8</v>
+        <v>129.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>231.1</v>
+        <v>31.4</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1255,34 +1251,38 @@
         <v>29.5</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>23.8</v>
+        <v>2.3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>97.2</v>
+      <c r="J10" s="8" t="n">
+        <v>860.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.9</v>
@@ -1294,25 +1294,25 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>164.2</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="8" t="n">
-        <v>282.2</v>
+      <c r="W10" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>216.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.8</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1328,67 +1328,71 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G11" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>48.3</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="M11" s="8" t="n">
+        <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>21.6</v>
+      </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>23.8</v>
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>26.7</v>
+        <v>65.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>14.8</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>26.8</v>
+        <v>22.7</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>181.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1404,56 +1408,62 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="11" t="n">
+      <c r="C12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.9</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>81.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="8" t="n">
+        <v>22.6</v>
+      </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>161.2</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1465,9 +1475,11 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>164.5</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1482,44 +1494,50 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>22.7</v>
+        <v>13.5</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+        <v>12.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="L13" s="8" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.8</v>
+        <v>25.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>46.4</v>
+        <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
@@ -1528,7 +1546,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1536,13 +1554,15 @@
       <c r="W13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1556,18 +1576,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="C14" s="3" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>49.5</v>
+        <v>14.2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>16.5</v>
@@ -1579,38 +1601,40 @@
         <v>20.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>923.4</v>
+      <c r="R14" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>25.2</v>
+        <v>15.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>22.8</v>
@@ -1619,9 +1643,11 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>951.4</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1636,69 +1662,75 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>4.5</v>
+      <c r="D15" s="9" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>16.8</v>
+        <v>2.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>4.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>38.2</v>
+        <v>58.2</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>9.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1713,7 +1745,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>140.8</v>
       </c>
       <c r="E16" s="10" t="n">
@@ -1723,59 +1755,59 @@
         <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4</v>
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>18.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>2.1</v>
+        <v>951.3</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>9455.200000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.5</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.3</v>
+        <v>1182.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>118.8</v>
+        <v>21314.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1949.2</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10.1</v>
+        <v>1158.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>1708.8</v>
-      </c>
+        <v>11274.6</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>1151</v>
+        <v>100.5</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1791,48 +1823,54 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D17" s="10" t="n">
-        <v>25.9</v>
+        <v>28.9</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>89.5</v>
+        <v>19.3</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>12.9</v>
+      <c r="H17" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>191.2</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>25.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>25.3</v>
+        <v>23.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>64.90000000000001</v>
@@ -1841,11 +1879,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>82.2</v>
+        <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>2</v>
@@ -1865,11 +1905,11 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>30.2</v>
+      <c r="D18" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>24.9</v>
@@ -1878,51 +1918,53 @@
         <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>11</v>
+        <v>19.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>228.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>2.4</v>
+        <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.8</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>85.2</v>
+        <v>24.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>1</v>
@@ -1942,8 +1984,8 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="9" t="n">
-        <v>95.05</v>
+      <c r="D19" s="8" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
@@ -1955,38 +1997,44 @@
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+        <v>27.9</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P19" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.2</v>
+        <v>18.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -1994,11 +2042,11 @@
       <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="8" t="n">
-        <v>21.8</v>
+      <c r="X19" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2014,9 +2062,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="D20" s="9" t="n">
-        <v>0.3</v>
+        <v>85.3</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.9</v>
@@ -2025,31 +2075,35 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>48.6</v>
+        <v>17.6</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>26.2</v>
+        <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
@@ -2058,22 +2112,22 @@
         <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.2</v>
+        <v>82.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>82.8</v>
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2091,19 +2145,19 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.3</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2112,45 +2166,45 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>13.4</v>
-      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="8" t="n">
-        <v>19.1</v>
+      <c r="R21" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>90.2</v>
-      </c>
+      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2168,68 +2222,70 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>17.2</v>
+        <v>29.9</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>91.2</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="8" t="n">
-        <v>39.9</v>
+      <c r="R22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>956.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>39.9</v>
+        <v>856.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>194.7</v>
+        <v>94.7</v>
       </c>
       <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2245,63 +2301,69 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="D23" s="10" t="n">
-        <v>1144.1</v>
+        <v>1944.6</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>290.4</v>
+        <v>910.4</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>112.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>57.2</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>220.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>72.5</v>
+      </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2464.4</v>
+        <v>21.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.9</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>931.6</v>
+        <v>931.2</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1121</v>
+        <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>9360.6</v>
+        <v>96</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1108.4</v>
+        <v>47.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.7</v>
+        <v>197.4</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>927.8</v>
+        <v>118.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>12.4</v>
@@ -2322,60 +2384,62 @@
       </c>
       <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="10" t="n">
-        <v>28.5</v>
+        <v>82.5</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>81.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>98.8</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>316.4</v>
+        <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>531.2</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>728.2</v>
+        <v>12.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>85.2</v>
-      </c>
+      <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
@@ -2397,66 +2461,66 @@
       <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="E25" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>1192.2</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>9</v>
+        <v>15.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>11.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>25.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>23.2</v>
+        <v>29.9</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>69.2</v>
+        <v>67.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>59.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2474,12 +2538,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2494,31 +2558,35 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>91.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>47.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>716.2</v>
+        <v>26.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2529,7 +2597,7 @@
       <c r="W26" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
@@ -2549,21 +2617,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D27" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2572,17 +2642,19 @@
         <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>49.4</v>
+        <v>4.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
@@ -2591,26 +2663,26 @@
         <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2627,69 +2699,71 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="D28" s="9" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G28" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="O28" s="3" t="n">
-        <v>119080.9</v>
+        <v>122.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>25.6</v>
+        <v>2.3</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>62.2</v>
+        <v>21.8</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>61.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2709,39 +2783,41 @@
       <c r="D29" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>24.3</v>
+      <c r="F29" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>91.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="8" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>40.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2756,19 +2832,19 @@
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>39.4</v>
+        <v>2.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X29" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2784,9 +2860,11 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="D30" s="10" t="n">
-        <v>19498.4</v>
+        <v>1948.4</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>89.59999999999999</v>
@@ -2801,51 +2879,53 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.3</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.7</v>
+        <v>12.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.4</v>
+        <v>18.6</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>41.2</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>120.7</v>
+        <v>920.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1112.3</v>
-      </c>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>112.9</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>126.4</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>153822.2</v>
+        <v>3322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.1</v>
+        <v>1088.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1104.2</v>
+        <v>1184.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>114.6</v>
+        <v>115.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.6</v>
+        <v>108.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>928.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2863,64 +2943,68 @@
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="10" t="n">
-        <v>29.7</v>
+        <v>39.7</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19.8</v>
+        <v>11.9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M31" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>25.9</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>26.3</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.3</v>
+        <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2937,26 +3021,26 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="11" t="n">
-        <v>32.8</v>
+      <c r="D32" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
@@ -2967,9 +3051,11 @@
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1219.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -2978,25 +3064,25 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>22.4</v>
+        <v>288.1</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3013,38 +3099,44 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="11" t="n">
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D33" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>25.3</v>
+        <v>18.9</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14.6</v>
+        <v>1.4</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>94.5</v>
+        <v>4.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>90.2</v>
+        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3059,22 +3151,22 @@
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
       <c r="V33" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="X33" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>168.8</v>
+        <v>165.8</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3090,15 +3182,17 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="11" t="n">
-        <v>92.09999999999999</v>
+      <c r="C34" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>41.8</v>
+      <c r="F34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
@@ -3107,25 +3201,31 @@
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>93.5</v>
+        <v>13.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="8" t="n">
-        <v>282.5</v>
+      <c r="M34" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3134,22 +3234,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>68.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="X34" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>16.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3166,20 +3266,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="11" t="n">
-        <v>30.4</v>
+      <c r="D35" s="9" t="n">
+        <v>0.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>18.4</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.2</v>
+        <v>10.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3193,10 +3293,14 @@
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>30.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>994.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3211,22 +3315,22 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>32</v>
+        <v>12.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.2</v>
+        <v>113.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3243,8 +3347,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
-        <v>23.6</v>
+      <c r="D36" s="3" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3255,14 +3359,14 @@
       <c r="G36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>51.4</v>
+      <c r="H36" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3271,18 +3375,20 @@
         <v>18.9</v>
       </c>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>470.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>231.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
@@ -3291,7 +3397,7 @@
         <v>12.6</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.3</v>
+        <v>2.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3299,11 +3405,11 @@
       <c r="W36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>85.2</v>
+      <c r="X36" s="3" t="n">
+        <v>55.7</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3324,16 +3430,16 @@
         <v>1161.5</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>92.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8711</v>
+        <v>818</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
@@ -3342,47 +3448,49 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>42.2</v>
+        <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>981.1</v>
+        <v>28.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>941</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O37" s="3" t="n">
         <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
+        <v>120.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>111</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>241.3</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>367.2</v>
+        <v>3672.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>37.2</v>
+        <v>537.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3399,40 +3507,42 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="11" t="n">
-        <v>42.1</v>
+      <c r="D38" s="10" t="n">
+        <v>12.3</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>51.5</v>
+        <v>524.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>41</v>
+        <v>50.7</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>91.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
@@ -3441,16 +3551,16 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>274.9</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>22.2</v>
+        <v>14.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3459,7 +3569,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3476,39 +3586,39 @@
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="8" t="n">
-        <v>32.6</v>
+      <c r="D39" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
+        <v>10.2</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>245.16</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
+        <v>68.2</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>81</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>11.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3516,17 +3626,17 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>22.6</v>
+      <c r="R39" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1948.2</v>
+        <v>61.6</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>28.6</v>
+        <v>21.8</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>82</v>
@@ -3535,11 +3645,9 @@
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>114.4</v>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3555,66 +3663,68 @@
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>89</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>25.4</v>
+      <c r="D40" s="3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>18.8</v>
+        <v>14.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J40" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>91</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="R40" s="8" t="n">
+      <c r="Q40" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>25.9</v>
+      <c r="W40" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3635,53 +3745,53 @@
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="8" t="n">
-        <v>32.4</v>
+        <v>21.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>19</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>28.6</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>15.4</v>
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>82</v>
+        <v>2.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>91</v>
+        <v>11.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
@@ -3690,10 +3800,10 @@
         <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3713,68 +3823,62 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="9" t="n">
-        <v>12.29</v>
+      <c r="D42" s="3" t="n">
+        <v>32.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>24.6</v>
+        <v>18.8</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>10.2</v>
+        <v>2.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>62.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>15.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M42" s="8" t="n">
-        <v>11.9</v>
+        <v>950.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>29.2</v>
+        <v>11.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>266.2</v>
+        <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="R42" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>271.2</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>216.7</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3789,10 +3893,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3826,10 +3932,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3865,64 +3973,68 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>32.3</v>
+        <v>122.3</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>18.7</v>
+        <v>24.6</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>25.5</v>
+        <v>182</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13.7</v>
+        <v>18.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>117.5</v>
+        <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>19.9</v>
+        <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.3</v>
+        <v>89</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>92.2</v>
+        <v>266.6</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>22.9</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>160.5</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9.9</v>
+        <v>509.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22.8</v>
+        <v>96.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.8</v>
+        <v>818.7</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>24.2</v>
+        <v>966.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>271.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>51.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3938,36 +4050,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="13" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>9885.5</v>
+      <c r="T46" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>116560.8</v>
+        <v>1211101.1</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -150,6 +156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,20 +772,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="9" t="n">
-        <v>91.7</v>
+      <c r="D4" s="3" t="n">
+        <v>31.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="9" t="n">
-        <v>84.5</v>
+      <c r="F4" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -794,10 +803,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.9</v>
+        <v>8.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -809,7 +818,7 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.9</v>
+        <v>25.2</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>45.2</v>
@@ -818,7 +827,7 @@
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -839,7 +848,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D5" s="3" t="n">
         <v>25.2</v>
       </c>
@@ -847,34 +858,34 @@
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>14.6</v>
+      <c r="M5" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -886,19 +897,19 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>21.8</v>
+        <v>43.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
@@ -924,16 +935,16 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
@@ -942,25 +953,25 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>15.4</v>
+        <v>17.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>97.5</v>
+        <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -972,22 +983,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>17.8</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1012,7 +1023,7 @@
       <c r="E7" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>2.5</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1041,35 +1052,37 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>24.2</v>
+        <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>87.2</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>114.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1084,15 +1097,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>82.59999999999999</v>
+      <c r="F8" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1101,10 +1116,10 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.4</v>
@@ -1132,13 +1147,13 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>24.6</v>
+        <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1147,10 +1162,10 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>59.2</v>
+        <v>69.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1166,17 +1181,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="F9" s="10" t="n">
+      <c r="E9" s="9" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>5.7</v>
@@ -1185,13 +1200,13 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>47.1</v>
+        <v>944.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1200,7 +1215,7 @@
         <v>100.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.6</v>
+        <v>452.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1212,16 +1227,16 @@
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>129.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>11</v>
@@ -1230,7 +1245,7 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1246,29 +1261,33 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="10" t="n">
+      <c r="C10" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>19.6</v>
+      <c r="G10" s="8" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>860.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
@@ -1276,7 +1295,7 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
@@ -1297,7 +1316,7 @@
         <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
@@ -1312,7 +1331,7 @@
         <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1334,62 +1353,60 @@
       <c r="E11" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>2.3</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>21.6</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>65.7</v>
+      <c r="R11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
+        <v>6.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
@@ -1409,22 +1426,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>5.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>81.5</v>
+        <v>17.3</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
@@ -1433,7 +1450,7 @@
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
@@ -1441,7 +1458,7 @@
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1451,34 +1468,34 @@
         <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.8</v>
+        <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>164.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1500,20 +1517,20 @@
       <c r="E13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>2.2</v>
+      <c r="F13" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>27.5</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -1525,7 +1542,7 @@
         <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1534,7 +1551,7 @@
         <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>20.4</v>
@@ -1546,7 +1563,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1576,9 +1593,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>133.1</v>
-      </c>
+      <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
@@ -1586,12 +1601,12 @@
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1607,28 +1622,26 @@
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
+        <v>19.7</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.4</v>
+        <v>31.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>88.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1643,10 +1656,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>17.2</v>
+        <v>717.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>951.4</v>
+        <v>51.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1661,12 +1674,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
-        <v>89.19</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>88.59999999999999</v>
+      <c r="C15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>29.5</v>
@@ -1678,28 +1693,28 @@
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.1</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>2.6</v>
@@ -1707,8 +1722,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>4.8</v>
+      <c r="S15" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1719,8 +1734,8 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>9.5</v>
+      <c r="W15" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
@@ -1729,7 +1744,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1745,29 +1760,29 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>116.6</v>
+      <c r="D16" s="9" t="n">
+        <v>1940.4</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
@@ -1779,35 +1794,35 @@
         <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9455.200000000001</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>16.2</v>
+        <v>122.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.9</v>
+        <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>21314.2</v>
+        <v>18.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1158.5</v>
+        <v>984.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>11274.6</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>100.5</v>
+        <v>10064.6</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1823,17 +1838,15 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E17" s="10" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="9" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>22.3</v>
+      <c r="F17" s="9" t="n">
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.6</v>
@@ -1845,41 +1858,39 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="M17" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>222.3</v>
+        <v>22.7</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>21.5</v>
@@ -1905,23 +1916,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="8" t="n">
-        <v>8.9</v>
+      <c r="D18" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.9</v>
+        <v>1.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.6</v>
@@ -1930,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
@@ -1943,7 +1954,7 @@
         <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2.1</v>
+        <v>29.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1952,16 +1963,16 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>54.8</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>24.3</v>
@@ -1983,9 +1994,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="C19" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
@@ -1997,7 +2010,7 @@
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.5</v>
+        <v>46.9</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.3</v>
@@ -2008,8 +2021,8 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>418.3</v>
+      <c r="L19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>18.2</v>
@@ -2028,13 +2041,13 @@
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2062,14 +2075,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>85.3</v>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
@@ -2093,9 +2104,11 @@
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O20" s="3" t="n">
         <v>90.2</v>
       </c>
@@ -2109,22 +2122,22 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41.8</v>
+        <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2144,8 +2157,8 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
-        <v>28.7</v>
+      <c r="D21" s="10" t="n">
+        <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2154,10 +2167,10 @@
         <v>21.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2166,7 +2179,7 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>19.4</v>
@@ -2182,19 +2195,19 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>13.5</v>
@@ -2222,25 +2235,25 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E22" s="9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="F22" s="8" t="n">
+        <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.2</v>
+        <v>23.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2249,10 +2262,10 @@
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>10.8</v>
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99.2</v>
@@ -2270,7 +2283,7 @@
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>856.2</v>
+        <v>8956.200000000001</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
@@ -2301,57 +2314,55 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>1944.6</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>910.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>112.8</v>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="9" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>220.8</v>
+        <v>85.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>72.5</v>
+        <v>2.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>21.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>931.2</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.2</v>
+        <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>47.9</v>
@@ -2360,13 +2371,13 @@
         <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>118.8</v>
+        <v>94927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2383,58 +2394,58 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="10" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
+      <c r="D24" s="9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="G24" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>58.9</v>
+        <v>8.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>88.8</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>531.2</v>
+        <v>581.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>21</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>12.2</v>
+        <v>78.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
-        <v>81.7</v>
+      <c r="V24" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>20.5</v>
@@ -2457,40 +2468,40 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E25" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>42.4</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>15.5</v>
+        <v>24.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2505,22 +2516,22 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>29.9</v>
+        <v>23.1</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>67.8</v>
+        <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>59.1</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2537,20 +2548,20 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="n">
-        <v>28.6</v>
+      <c r="D26" s="10" t="n">
+        <v>98.59999999999999</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2559,34 +2570,32 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>2.3</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>71.8</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>47.9</v>
+        <v>27.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>26.2</v>
+        <v>76.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2617,53 +2626,51 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="9" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>91.2</v>
+        <v>18.8</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2672,9 +2679,9 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V27" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W27" s="3" t="inlineStr"/>
@@ -2682,7 +2689,7 @@
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2699,44 +2706,44 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F28" s="3" t="n">
+      <c r="D28" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>21.1</v>
+        <v>0.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>122.2</v>
+        <v>1272.4</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
@@ -2744,26 +2751,26 @@
       <c r="R28" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>74</v>
+      <c r="S28" s="3" t="n">
+        <v>27.6</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>61.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>17.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2786,17 +2793,17 @@
       <c r="E29" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2808,13 +2815,11 @@
         <v>19.2</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>4.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8</v>
@@ -2825,7 +2830,7 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2838,13 +2843,13 @@
         <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2860,17 +2865,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1948.4</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>118.1</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="9" t="n">
+        <v>149.4</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2885,47 +2888,47 @@
         <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>12.4</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>920.7</v>
+        <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>3322.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1088.1</v>
+        <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1184.1</v>
+        <v>18.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>108.4</v>
+        <v>374.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2942,14 +2945,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="10" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>23.8</v>
+      <c r="D31" s="9" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>11.9</v>
@@ -2964,35 +2967,35 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>1</v>
+      <c r="L31" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>22.5</v>
+      <c r="R31" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.6</v>
@@ -3004,7 +3007,7 @@
         <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>14.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -3022,40 +3025,38 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E32" s="9" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>2.5</v>
+      <c r="F32" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="H32" s="8" t="n">
-        <v>11.8</v>
+      <c r="H32" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -3064,15 +3065,15 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="U32" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
@@ -3082,7 +3083,7 @@
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3099,16 +3100,14 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>32.6</v>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="10" t="n">
+        <v>4.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F33" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="10" t="n">
         <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3118,7 +3117,7 @@
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.5</v>
@@ -3126,17 +3125,15 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="M33" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3145,28 +3142,28 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.6</v>
+        <v>12.8</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>165.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3182,14 +3179,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>25.8</v>
@@ -3204,28 +3199,28 @@
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>51.1</v>
+      <c r="M34" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3234,10 +3229,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3249,7 +3244,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3266,20 +3261,20 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="9" t="n">
-        <v>0.4</v>
+      <c r="D35" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>0.8</v>
+        <v>19.4</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>10.2</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3291,16 +3286,16 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>30.1</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>994.2</v>
+        <v>172.4</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3315,13 +3310,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>12.2</v>
+        <v>192.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3330,7 +3325,7 @@
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>113.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3347,26 +3342,26 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="n">
-        <v>33.6</v>
+      <c r="D36" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3374,12 +3369,12 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>470.6</v>
+        <v>70.7</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3388,13 +3383,13 @@
         <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>2.8</v>
@@ -3406,10 +3401,10 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>55.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3426,71 +3421,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="10" t="n">
-        <v>1161.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="D37" s="9" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>9.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>818</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>949.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.6</v>
+        <v>950.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.6</v>
+        <v>1230.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.1</v>
+        <v>12.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3672.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>537.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3507,39 +3502,39 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>524.6</v>
+      <c r="F38" s="9" t="n">
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H38" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>7.2</v>
+        <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>50.7</v>
+        <v>30.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
@@ -3551,7 +3546,7 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>14.9</v>
@@ -3560,7 +3555,7 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3569,7 +3564,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3590,35 +3585,35 @@
         <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>18.5</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>19</v>
+        <v>17.9</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>81</v>
+        <v>19.9</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>13</v>
+        <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>796</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3626,26 +3621,26 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.6</v>
+        <v>69.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
@@ -3669,23 +3664,23 @@
       <c r="E40" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="9" t="n">
-        <v>85.40000000000001</v>
+      <c r="F40" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
@@ -3693,8 +3688,8 @@
       <c r="M40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>11.8</v>
+      <c r="N40" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3702,17 +3697,17 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>60.8</v>
+      <c r="Q40" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>192.6</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>22.8</v>
@@ -3720,11 +3715,11 @@
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>51.8</v>
+      <c r="W40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>8.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3744,11 +3739,11 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>19</v>
+      <c r="E41" s="10" t="n">
+        <v>17.9</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.4</v>
@@ -3763,24 +3758,22 @@
         <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>4.9</v>
+      <c r="L41" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
         <v>2.4</v>
       </c>
@@ -3791,19 +3784,19 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>2.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3826,36 +3819,34 @@
       <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>2.5</v>
+      <c r="E42" s="10" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="L42" s="8" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -3868,12 +3859,14 @@
       <c r="R42" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="S42" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="8" t="n">
-        <v>1</v>
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="V42" s="3" t="inlineStr"/>
       <c r="W42" s="3" t="inlineStr"/>
@@ -3896,9 +3889,9 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="11" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3935,9 +3928,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3972,41 +3965,41 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="9" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>182</v>
+      <c r="F45" s="9" t="n">
+        <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>18.8</v>
+        <v>5.4</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.1</v>
+        <v>141.1</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>89</v>
+        <v>8.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>266.6</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -4019,22 +4012,22 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>509.7</v>
+        <v>32.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>818.7</v>
+        <v>22.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>966.3</v>
+        <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>271.2</v>
+        <v>221.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4051,17 +4044,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>93.7</v>
+        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
@@ -4069,21 +4062,23 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
-        <v>18.1</v>
+      <c r="J46" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>42.7</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>19.3</v>
+        <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4106,10 +4101,10 @@
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1211101.1</v>
+        <v>87208.5</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +164,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,10 +808,10 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -811,7 +823,7 @@
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -875,10 +887,10 @@
       <c r="K5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -890,7 +902,7 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -905,7 +917,7 @@
       <c r="U5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="10" t="n">
         <v>43.9</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -958,10 +970,10 @@
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -973,7 +985,7 @@
       <c r="P6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="11" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1029,7 +1041,7 @@
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="12" t="n">
         <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1041,10 +1053,10 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
@@ -1054,7 +1066,7 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="11" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
@@ -1124,10 +1136,10 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1137,7 +1149,7 @@
       <c r="P8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="R8" s="3" t="n">
@@ -1152,7 +1164,7 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1202,13 +1214,13 @@
       <c r="J9" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>944.1</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>92.8</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1220,10 +1232,10 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1235,10 +1247,10 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>11</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1273,7 +1285,7 @@
       <c r="F10" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="12" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1288,10 +1300,10 @@
       <c r="K10" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1303,10 +1315,10 @@
       <c r="P10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1318,10 +1330,10 @@
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1356,13 +1368,13 @@
       <c r="F11" s="10" t="n">
         <v>2.3</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="12" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
@@ -1371,10 +1383,10 @@
       <c r="K11" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1387,7 +1399,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="10" t="n">
         <v>2.3</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1402,7 +1414,7 @@
       <c r="V11" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="11" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1485,7 +1497,7 @@
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1535,7 +1547,7 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1568,7 +1580,7 @@
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1646,10 +1658,10 @@
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1716,13 +1728,13 @@
       <c r="P15" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="12" t="n">
         <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
@@ -1734,7 +1746,7 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1781,13 +1793,13 @@
       <c r="J16" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="9" t="n">
         <v>951.3</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="9" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1799,10 +1811,10 @@
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>122.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1814,10 +1826,10 @@
       <c r="U16" s="3" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>984.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
@@ -1861,10 +1873,10 @@
         <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -1874,13 +1886,13 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="9" t="n">
         <v>51.8</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="12" t="n">
         <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1889,10 +1901,10 @@
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1940,10 +1952,10 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
@@ -2021,7 +2033,7 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2100,7 +2112,7 @@
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="11" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2115,7 +2127,7 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2130,7 +2142,7 @@
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2181,7 +2193,7 @@
       <c r="K21" s="3" t="n">
         <v>73.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2197,7 +2209,7 @@
       <c r="Q21" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="10" t="n">
         <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2240,7 +2252,7 @@
       <c r="E22" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="12" t="n">
         <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2258,7 +2270,7 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2276,7 +2288,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="10" t="n">
         <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2336,13 +2348,13 @@
       <c r="J23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="9" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2352,10 +2364,10 @@
         <v>43.1</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2367,10 +2379,10 @@
       <c r="U23" s="3" t="n">
         <v>47.9</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>108.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2416,10 +2428,10 @@
         <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>88.8</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
@@ -2429,13 +2441,13 @@
       <c r="P24" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="12" t="n">
         <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
@@ -2444,10 +2456,10 @@
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
@@ -2493,10 +2505,10 @@
       <c r="K25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="10" t="n">
         <v>42.4</v>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="13" t="inlineStr"/>
       <c r="N25" s="3" t="n">
         <v>1.4</v>
       </c>
@@ -2527,7 +2539,7 @@
       <c r="W25" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="12" t="n">
         <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2657,7 +2669,7 @@
       <c r="M27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="12" t="n">
         <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2666,7 +2678,7 @@
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2684,7 +2696,7 @@
       <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="3" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
@@ -2748,7 +2760,7 @@
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="10" t="n">
         <v>2.3</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2763,7 +2775,7 @@
       <c r="V28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="12" t="n">
         <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2814,7 +2826,7 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>1.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2887,13 +2899,13 @@
       <c r="J30" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -2903,10 +2915,10 @@
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2918,10 +2930,10 @@
       <c r="U30" s="3" t="n">
         <v>118.2</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2967,10 +2979,10 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -2982,10 +2994,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="9" t="n">
         <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -2997,10 +3009,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3061,10 +3073,10 @@
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="11" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3079,7 +3091,7 @@
       <c r="V32" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3125,7 +3137,7 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3138,10 +3150,10 @@
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3156,7 +3168,7 @@
       <c r="V33" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3207,7 +3219,7 @@
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="10" t="n">
         <v>91.90000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3219,10 +3231,10 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3237,7 +3249,7 @@
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3300,10 +3312,10 @@
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3318,7 +3330,7 @@
       <c r="V35" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="11" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3369,7 +3381,7 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
@@ -3379,10 +3391,10 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3397,7 +3409,7 @@
       <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="11" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3442,13 +3454,13 @@
       <c r="J37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>949.9</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3460,10 +3472,10 @@
       <c r="P37" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="11" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3475,10 +3487,10 @@
       <c r="U37" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3524,10 +3536,10 @@
         <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3539,10 +3551,10 @@
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3554,10 +3566,10 @@
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3608,7 +3620,7 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3621,7 +3633,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="10" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3697,10 +3709,10 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
+      <c r="Q40" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="10" t="n">
         <v>82.2</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3789,7 +3801,7 @@
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="10" t="n">
         <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3840,7 +3852,7 @@
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3856,7 +3868,7 @@
       <c r="Q42" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -3868,8 +3880,8 @@
       <c r="U42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
+      <c r="V42" s="13" t="inlineStr"/>
+      <c r="W42" s="13" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3889,26 +3901,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -3928,26 +3940,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="13" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -3986,13 +3998,13 @@
       <c r="J45" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>141.1</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4004,8 +4016,8 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="n">
+      <c r="Q45" s="14" t="inlineStr"/>
+      <c r="R45" s="9" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4017,10 +4029,10 @@
       <c r="U45" s="3" t="n">
         <v>95.2</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4062,16 +4074,16 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="8" t="n">
+      <c r="J46" s="12" t="n">
         <v>4.1</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="9" t="n">
         <v>42.7</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4084,7 +4096,7 @@
         <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -4094,10 +4106,10 @@
       <c r="U46" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,9 +162,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -785,7 +782,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>31.7</v>
+        <v>39.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
@@ -808,17 +805,17 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>8.4</v>
+        <v>28.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.8</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -830,18 +827,18 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>45.2</v>
+        <v>4.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="11" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -860,35 +857,33 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>17.6</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>17.6</v>
@@ -912,22 +907,22 @@
         <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>10.2</v>
+        <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="10" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W5" s="11" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>16.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -949,10 +944,10 @@
       <c r="D6" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E6" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -965,25 +960,25 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="M6" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>921.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="11" t="n">
         <v>29.5</v>
@@ -995,22 +990,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>20.6</v>
+        <v>390.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>21.3</v>
+      <c r="W6" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>17.8</v>
+        <v>27.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1029,20 +1024,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>2.5</v>
+      <c r="F7" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>79.8</v>
+      <c r="H7" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1051,17 +1046,19 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L7" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
@@ -1076,7 +1073,7 @@
         <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>87.2</v>
+        <v>81.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
@@ -1084,17 +1081,17 @@
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="11" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>23.8</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1109,17 +1106,15 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>22.6</v>
+      <c r="F8" s="10" t="n">
+        <v>42.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1128,7 +1123,7 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.2</v>
@@ -1136,7 +1131,7 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M8" s="11" t="n">
@@ -1144,10 +1139,10 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>91.2</v>
+        <v>791.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="11" t="n">
         <v>25.8</v>
@@ -1159,25 +1154,25 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>6.6</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W8" s="3" t="n">
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W8" s="11" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>69.2</v>
+        <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.3</v>
+        <v>27.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,40 +1189,40 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="9" t="n">
-        <v>147.4</v>
+        <v>147.9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>54.8</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>944.1</v>
+        <v>44.1</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>92.59999999999999</v>
+        <v>3972.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>100.1</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>452.5</v>
+        <v>451.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1236,10 +1231,10 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>110.9</v>
+        <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122</v>
+        <v>122.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
@@ -1257,9 +1252,11 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1273,47 +1270,45 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="9" t="n">
         <v>29.5</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G10" s="12" t="n">
-        <v>91.59999999999999</v>
+      <c r="G10" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" s="11" t="n">
         <v>25.9</v>
@@ -1325,7 +1320,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1333,17 +1328,17 @@
       <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="11" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.2</v>
+        <v>62.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1359,63 +1354,59 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="8" t="n">
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G11" s="12" t="n">
+      <c r="F11" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>18.3</v>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="10" t="n">
-        <v>2.3</v>
+      <c r="R11" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>26.8</v>
@@ -1423,7 +1414,9 @@
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1437,9 +1430,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
@@ -1450,37 +1441,37 @@
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>984.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.6</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.6</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1489,25 +1480,25 @@
         <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="11" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>24.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>83.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.5</v>
+        <v>82.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1527,13 +1518,13 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.9</v>
+        <v>89.3</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1542,22 +1533,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="12" t="n">
-        <v>19.2</v>
+      <c r="L13" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.3</v>
+        <v>0.4</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1575,7 +1566,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>31.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1587,10 +1578,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85.2</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1605,7 +1596,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
@@ -1619,24 +1612,26 @@
         <v>19.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
       </c>
@@ -1650,16 +1645,16 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.6</v>
+        <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>88.2</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="12" t="n">
-        <v>15.1</v>
+      <c r="V14" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="W14" s="11" t="n">
         <v>22.8</v>
@@ -1668,7 +1663,7 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>717.2</v>
+        <v>27.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>51.4</v>
@@ -1686,32 +1681,30 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>29.5</v>
+      <c r="F15" s="10" t="n">
+        <v>93.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
@@ -1720,13 +1713,13 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" s="10" t="n">
         <v>2.6</v>
@@ -1734,8 +1727,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <v>22.7</v>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1744,7 +1737,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="W15" s="11" t="n">
         <v>20.9</v>
@@ -1756,7 +1749,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1773,70 +1766,72 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="9" t="n">
-        <v>1940.4</v>
+        <v>14</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>44.3</v>
+        <v>112.3</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>114.6</v>
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>48.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>3.2</v>
-      </c>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
       <c r="L16" s="9" t="n">
-        <v>951.3</v>
+        <v>95.3</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>853.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>122.2</v>
+        <v>127.2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>1127.3</v>
+        <v>122.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>18.2</v>
+        <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>984.8</v>
+        <v>187.8</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>124.6</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>10064.6</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>970.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1852,16 +1847,16 @@
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="9" t="n">
-        <v>29.9</v>
+        <v>28.4</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>23.3</v>
+        <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1870,39 +1865,41 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.8</v>
+        <v>22.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>51.8</v>
+        <v>25.8</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="12" t="n">
-        <v>35.3</v>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="W17" s="11" t="n">
         <v>21.5</v>
@@ -1911,9 +1908,11 @@
         <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1932,41 +1931,43 @@
         <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>91.2</v>
+        <v>291.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>29.2</v>
+      <c r="Q18" s="10" t="n">
+        <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1975,10 +1976,10 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>1</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
@@ -1987,12 +1988,14 @@
         <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="Y18" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="Z18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2007,25 +2010,25 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>24.1</v>
+      <c r="F19" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.9</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>2.5</v>
@@ -2033,13 +2036,15 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2059,21 +2064,23 @@
         <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>19.9</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2087,18 +2094,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="D20" s="3" t="n">
-        <v>22.3</v>
+        <v>28.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>9.6</v>
+      <c r="G20" s="8" t="n">
+        <v>59.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2110,19 +2119,17 @@
         <v>2.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
-        <v>90.2</v>
+        <v>99.2</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0</v>
@@ -2134,27 +2141,29 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>72.2</v>
+        <v>22.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="10" t="n">
-        <v>81.8</v>
+      <c r="V20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="3" t="n">
-        <v>22.1</v>
+      <c r="X20" s="8" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2168,21 +2177,23 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="10" t="n">
-        <v>1.5</v>
+      <c r="C21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2191,9 +2202,9 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="L21" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2207,31 +2218,35 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>11.2</v>
+        <v>19.2</v>
       </c>
       <c r="R21" s="10" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="W21" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2245,15 +2260,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D22" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>32.8</v>
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
@@ -2265,54 +2282,56 @@
         <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="11" t="n">
-        <v>18</v>
+      <c r="L22" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>0.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.2</v>
+        <v>991.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+      <c r="Q22" s="10" t="n">
+        <v>2.9</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8956.200000000001</v>
+        <v>86.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>24.6</v>
+      <c r="V22" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="W22" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="Y22" s="3" t="n">
         <v>80.2</v>
       </c>
-      <c r="Y22" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2328,70 +2347,72 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="9" t="n">
-        <v>194.4</v>
+        <v>1942.6</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>10.4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>119.2</v>
+        <v>112.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.8</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L23" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L23" s="9" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>92.90000000000001</v>
+        <v>1952.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>43.1</v>
+        <v>951.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>107.9</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>47.9</v>
+        <v>37.7</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>108.6</v>
+        <v>108.4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>19.7</v>
+        <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94927.8</v>
+        <v>198.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>9425.6</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2405,7 +2426,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D24" s="9" t="n">
         <v>28.5</v>
       </c>
@@ -2422,36 +2445,40 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="L24" s="9" t="n">
-        <v>88.8</v>
+        <v>98.8</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>581.2</v>
+        <v>91.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="12" t="n">
-        <v>823.9</v>
+        <v>21.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.2</v>
+        <v>72.3</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2462,11 +2489,15 @@
       <c r="W24" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="X24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2480,70 +2511,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="O25" s="3" t="n">
-        <v>24.2</v>
+        <v>59.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V25" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X25" s="12" t="n">
-        <v>71.3</v>
+      <c r="W25" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>69.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2559,18 +2592,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="10" t="n">
-        <v>98.59999999999999</v>
+      <c r="C26" s="3" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1.6</v>
@@ -2582,17 +2617,19 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>98.96000000000001</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2601,10 +2638,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2612,11 +2649,11 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>21.3</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>86.2</v>
@@ -2624,7 +2661,9 @@
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2649,40 +2688,40 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.9</v>
+        <v>19.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>11.8</v>
+      <c r="M27" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.4</v>
+        <v>922.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="10" t="n">
-        <v>2.6</v>
+      <c r="Q27" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2691,19 +2730,23 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="13" t="inlineStr"/>
       <c r="X27" s="3" t="n">
-        <v>80.2</v>
+        <v>24</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>80.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2718,17 +2761,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="E28" s="10" t="n">
-        <v>1.5</v>
+      <c r="E28" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2740,51 +2783,53 @@
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>16.2</v>
+        <v>0.3</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.1</v>
+        <v>14.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1272.4</v>
+        <v>92.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R28" s="10" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>40.2</v>
+        <v>4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>22.8</v>
+      <c r="V28" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="W28" s="10" t="n">
+        <v>2.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.4</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>53.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2806,19 +2851,19 @@
         <v>18.4</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
@@ -2826,15 +2871,15 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="M29" s="13" t="inlineStr"/>
+      <c r="N29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>40.7</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2843,7 +2888,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
@@ -2851,8 +2896,8 @@
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>20.1</v>
+      <c r="V29" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2863,7 +2908,9 @@
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2879,16 +2926,16 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="9" t="n">
-        <v>149.4</v>
+        <v>1498.4</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>8.9</v>
+        <v>189.6</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>119.1</v>
+        <v>11.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>5.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
@@ -2897,20 +2944,20 @@
         <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.8</v>
+        <v>17.8</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>92.5</v>
+        <v>292.5</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>96.09999999999999</v>
+        <v>392.1</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2919,7 +2966,7 @@
         <v>130.7</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>112.7</v>
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
@@ -2931,18 +2978,20 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>18.4</v>
+        <v>104.1</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>117.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>374.2</v>
+        <v>312.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2961,22 +3010,22 @@
         <v>29.7</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.9</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
@@ -2986,7 +3035,7 @@
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -2995,33 +3044,35 @@
         <v>0</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>82.8</v>
+        <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>25.6</v>
+      <c r="V31" s="11" t="n">
+        <v>20.8</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>77.3</v>
+        <v>22.7</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>23.6</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3035,69 +3086,73 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>34.8</v>
+      <c r="C32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>23.28</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>25.6</v>
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>29.1</v>
+        <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q32" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="11" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.2</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>22.2</v>
+      <c r="V32" s="10" t="n">
+        <v>2.2</v>
       </c>
       <c r="W32" s="11" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+        <v>85.3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>22.4</v>
+      </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3112,9 +3167,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D33" s="10" t="n">
-        <v>4.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
@@ -3137,36 +3194,36 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>18.8</v>
+      <c r="M33" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="11" t="n">
+      <c r="Q33" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="11" t="n">
-        <v>27.8</v>
+      <c r="R33" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>12.8</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="W33" s="11" t="n">
         <v>27.4</v>
@@ -3177,7 +3234,9 @@
       <c r="Y33" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3196,15 +3255,15 @@
         <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3214,37 +3273,37 @@
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>91.90000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q34" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R34" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2</v>
+        <v>23.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3256,9 +3315,11 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3272,7 +3333,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3298,31 +3361,31 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>11.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>1.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>172.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>192.2</v>
+        <v>129.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
@@ -3339,7 +3402,9 @@
       <c r="Y35" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3354,11 +3419,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="10" t="n">
-        <v>1.3</v>
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
@@ -3373,38 +3438,40 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>70.7</v>
+        <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="11" t="n">
-        <v>23</v>
+      <c r="R36" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.5</v>
+        <v>48.2</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.8</v>
+        <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3413,12 +3480,14 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>8.5</v>
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3437,7 +3506,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>92.09999999999999</v>
+        <v>1929.5</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>126.9</v>
@@ -3446,60 +3515,62 @@
         <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>949.9</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>98.09999999999999</v>
+        <v>951.1</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>92</v>
+        <v>0.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.2</v>
+        <v>150.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q37" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Q37" s="9" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>119</v>
+        <v>117.3</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1230.4</v>
+        <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>12.4</v>
+        <v>124.7</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>115</v>
-      </c>
-      <c r="W37" s="9" t="n">
-        <v>129.9</v>
+        <v>111</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="n">
+        <v>247.3</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3521,7 +3592,7 @@
         <v>18.4</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>25.4</v>
+        <v>2.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3533,41 +3604,41 @@
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="9" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>46.8</v>
+        <v>17.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.2</v>
+        <v>18.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>30.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q38" s="11" t="n">
+      <c r="Q38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>22.2</v>
+        <v>82.2</v>
       </c>
       <c r="W38" s="11" t="n">
         <v>25.2</v>
@@ -3576,9 +3647,11 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3594,38 +3667,38 @@
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>18.5</v>
+        <v>32.6</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L39" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>796</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3633,29 +3706,33 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="10" t="n">
-        <v>42.6</v>
+      <c r="R39" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.1</v>
+        <v>22.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>27.8</v>
+        <v>21.9</v>
       </c>
       <c r="V39" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W39" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z39" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3669,39 +3746,41 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D40" s="3" t="n">
         <v>32.5</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>25.4</v>
+      <c r="F40" s="10" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>13.8</v>
+      <c r="M40" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3709,34 +3788,36 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R40" s="10" t="n">
-        <v>82.2</v>
+      <c r="Q40" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>8.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="n">
+        <v>826.2</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3752,10 +3833,10 @@
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>17.9</v>
+        <v>31.8</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.4</v>
@@ -3764,30 +3845,32 @@
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.9</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q41" s="3" t="n">
-        <v>2.4</v>
+        <v>29.4</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3796,24 +3879,26 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2.4</v>
+        <v>37.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V41" s="10" t="n">
-        <v>2.4</v>
+        <v>9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>68.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3828,60 +3913,64 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="10" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>8.6</v>
+      <c r="J42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="10" t="n">
-        <v>98.40000000000001</v>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>25</v>
+      <c r="Q42" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="R42" s="10" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" s="13" t="inlineStr"/>
-      <c r="W42" s="13" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="V42" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3914,7 +4003,7 @@
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
       <c r="R43" s="13" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -3953,7 +4042,7 @@
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
       <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -3984,64 +4073,66 @@
         <v>24.6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>5.4</v>
+        <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>62.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>141.1</v>
+        <v>111.4</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>8.9</v>
-      </c>
+        <v>111.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>2366.2</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="14" t="inlineStr"/>
+      <c r="Q45" s="9" t="n">
+        <v>106.9</v>
+      </c>
       <c r="R45" s="9" t="n">
-        <v>91.59999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>32.7</v>
+        <v>132.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.2</v>
+        <v>1.8</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>22.9</v>
+        <v>892.7</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>221.2</v>
+        <v>19327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4057,68 +4148,72 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="9" t="n">
-        <v>22.3</v>
+        <v>1.1</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>18.7</v>
+        <v>32.3</v>
       </c>
       <c r="F46" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>42.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>87208.5</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="n">
+        <v>992.9</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>16.9</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -805,29 +805,29 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>4.5</v>
@@ -835,10 +835,10 @@
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V4" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W4" s="11" t="n">
+      <c r="V4" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W4" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -858,17 +858,17 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -882,25 +882,25 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M5" s="11" t="n">
+      <c r="L5" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M5" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -910,19 +910,19 @@
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="E6" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -963,49 +963,49 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="9" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.8</v>
+        <v>14.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>921.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>24.9</v>
+      <c r="R6" s="9" t="n">
+        <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>390.6</v>
+        <v>50.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
@@ -1037,7 +1037,7 @@
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1046,12 +1046,12 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1063,25 +1063,25 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
+        <v>87.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>42.6</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1131,23 +1131,23 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>791.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1159,10 +1159,10 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1172,7 +1172,7 @@
         <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="9" t="n">
-        <v>147.9</v>
-      </c>
-      <c r="E9" s="9" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1207,30 +1207,30 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K9" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>44.1</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>3972.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="10" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="10" t="n">
         <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1245,8 +1245,8 @@
       <c r="V9" s="9" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>11</v>
+      <c r="W9" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1277,8 +1277,8 @@
       <c r="E10" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>2.3</v>
+      <c r="F10" s="10" t="n">
+        <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>11.6</v>
@@ -1290,7 +1290,7 @@
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
@@ -1298,19 +1298,19 @@
       <c r="L10" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="9" t="n">
         <v>25.9</v>
       </c>
       <c r="R10" s="9" t="n">
@@ -1320,7 +1320,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>6.4</v>
+        <v>64</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1328,17 +1328,17 @@
       <c r="V10" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="F11" s="3" t="n">
@@ -1368,15 +1368,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1385,13 +1385,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>29.8</v>
+      <c r="R11" s="9" t="n">
+        <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
@@ -1405,7 +1405,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="11" t="n">
+      <c r="W11" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,74 +1431,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>984.1</v>
+        <v>8.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2.5</v>
+        <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="11" t="n">
-        <v>21.9</v>
+      <c r="W12" s="9" t="n">
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1514,17 +1514,17 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.5</v>
+      <c r="E13" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>89.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1533,55 +1533,55 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.2</v>
+        <v>84.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="11" t="n">
+      <c r="W13" s="9" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>15.5</v>
@@ -1621,7 +1621,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1630,7 +1630,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1638,17 +1638,17 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="R14" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1656,17 +1656,17 @@
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="11" t="n">
+      <c r="W14" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1682,23 +1682,23 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>93.5</v>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1713,7 +1713,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1721,14 +1721,14 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1737,9 +1737,9 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W15" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1749,7 +1749,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1766,47 +1766,47 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>116.6</v>
+        <v>140.4</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>116.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="10" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="10" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>53.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="9" t="n">
-        <v>127.2</v>
+      <c r="Q16" s="10" t="n">
+        <v>122.2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>122.3</v>
+        <v>112.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1815,19 +1815,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>187.8</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>10.8</v>
+        <v>49.2</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>10.2</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1845,18 +1845,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="D17" s="9" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F17" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1865,20 +1867,20 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="9" t="n">
-        <v>18.5</v>
+      <c r="M17" s="10" t="n">
+        <v>18.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1893,15 +1895,15 @@
         <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="V17" s="9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="10" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1940,7 +1942,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1951,22 +1953,22 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="10" t="n">
-        <v>1.3</v>
+      <c r="M18" s="11" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="11" t="n">
         <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -1981,7 +1983,7 @@
       <c r="U18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2013,19 +2015,19 @@
         <v>1.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>2.4</v>
+      <c r="F19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -2036,14 +2038,14 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2061,22 +2063,22 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V19" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2095,19 +2097,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>59.6</v>
+      <c r="G20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2121,11 +2123,11 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.8</v>
+      <c r="L20" s="9" t="n">
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
@@ -2134,29 +2136,29 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="11" t="n">
         <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>23.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="8" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2181,7 +2183,7 @@
         <v>1.1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2204,13 +2206,15 @@
       <c r="K21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2220,29 +2224,29 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="10" t="n">
-        <v>1.3</v>
+      <c r="R21" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>12.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2267,19 +2271,19 @@
         <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>2.3</v>
+        <v>17.2</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
@@ -2287,38 +2291,38 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="10" t="n">
-        <v>1.8</v>
+      <c r="L22" s="9" t="n">
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>991.2</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>2.2</v>
+      <c r="Q22" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V22" s="10" t="n">
-        <v>2.4</v>
+      <c r="V22" s="9" t="n">
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2346,47 +2350,47 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="9" t="n">
-        <v>1942.6</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>112.2</v>
+      <c r="D23" s="10" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>12.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="L23" s="9" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>1952.9</v>
+      <c r="K23" s="10" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>458.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="10" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2398,17 +2402,17 @@
       <c r="U23" s="3" t="n">
         <v>37.7</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="10" t="n">
         <v>108.4</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="10" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>27.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2427,15 +2431,15 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2445,40 +2449,40 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>991999.1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M24" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M24" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="9" t="n">
-        <v>21.6</v>
+      <c r="R24" s="10" t="n">
+        <v>2.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2486,7 +2490,7 @@
       <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2496,7 +2500,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2512,20 +2516,20 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.1</v>
@@ -2536,47 +2540,47 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>12.9</v>
+      <c r="L25" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>59.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="11" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2593,22 +2597,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>29.6</v>
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>28.6</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F26" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>28.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2619,17 +2623,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="10" t="n">
-        <v>98.96000000000001</v>
+      <c r="M26" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2641,7 +2645,7 @@
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2649,7 +2653,7 @@
       <c r="U26" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2678,47 +2682,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="9" t="n">
         <v>27.3</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>19.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2727,12 +2731,12 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>2.5</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2761,17 +2765,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="9" t="n">
         <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2785,23 +2789,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M28" s="10" t="n">
-        <v>1.6</v>
+      <c r="L28" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2810,19 +2814,19 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W28" s="10" t="n">
-        <v>2.1</v>
+      <c r="W28" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2844,13 +2848,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="9" t="n">
         <v>30.1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2868,15 +2872,15 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>19.2</v>
+      <c r="L29" s="9" t="n">
+        <v>18.2</v>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2888,16 +2892,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>14.5</v>
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>13.4</v>
+      <c r="V29" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2909,7 +2913,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2926,68 +2930,68 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="9" t="n">
-        <v>1498.4</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>189.6</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>11.8</v>
+        <v>148.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.8</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="10" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>392.1</v>
+      <c r="L30" s="10" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="10" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>112.9</v>
+      <c r="R30" s="10" t="n">
+        <v>12.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>222.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="V30" s="9" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="W30" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W30" s="10" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -3009,33 +3013,33 @@
       <c r="D31" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F31" s="11" t="n">
+      <c r="E31" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M31" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M31" s="10" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.4</v>
+        <v>2.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3043,10 +3047,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="R31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="R31" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3058,14 +3062,14 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>47.8</v>
+      <c r="W31" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3089,44 +3093,44 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>23.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+      <c r="D32" s="3" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E32" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="11" t="n">
         <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3136,22 +3140,22 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="11" t="n">
+      <c r="V32" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W32" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>85.3</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3168,19 +3172,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>92.59999999999999</v>
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>2.5</v>
+      <c r="F33" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3191,48 +3195,48 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M33" s="10" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>78.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W33" s="11" t="n">
+      <c r="V33" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W33" s="9" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>15</v>
@@ -3250,7 +3254,9 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
       </c>
@@ -3258,12 +3264,12 @@
         <v>19.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3272,26 +3278,26 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3300,22 +3306,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="V34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="11" t="n">
+      <c r="W34" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9</v>
@@ -3334,13 +3340,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>27.4</v>
@@ -3357,25 +3363,25 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="10" t="n">
-        <v>1.3</v>
+      <c r="M35" s="11" t="n">
+        <v>1.8</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3385,15 +3391,15 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>15.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="W35" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3403,7 +3409,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3419,8 +3425,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="8" t="n">
-        <v>33.6</v>
+      <c r="D36" s="11" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3440,47 +3446,47 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>35</v>
+      <c r="R36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>4.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="11" t="n">
+      <c r="W36" s="9" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>85.2</v>
+        <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
@@ -3502,13 +3508,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="10" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>1929.5</v>
-      </c>
-      <c r="F37" s="9" t="n">
+      <c r="E37" s="10" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F37" s="10" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3524,52 +3530,52 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>949.9</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>951.1</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>0.1</v>
+        <v>49.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>2.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>50.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="9" t="n">
-        <v>117.3</v>
+      <c r="R37" s="10" t="n">
+        <v>17.5</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="W37" s="11" t="n">
+      <c r="W37" s="9" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3585,14 +3591,14 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="9" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="10" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>2.5</v>
+      <c r="F38" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3606,26 +3612,28 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>17.8</v>
+      <c r="K38" s="3" t="n">
+        <v>555.5</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3638,19 +3646,19 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="W38" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>13.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3677,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="11" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3678,7 +3686,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3687,18 +3695,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="10" t="n">
-        <v>49</v>
+      <c r="K39" s="9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3710,7 +3718,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>23.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3721,14 +3729,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="10" t="n">
-        <v>2.4</v>
+      <c r="W39" s="11" t="n">
+        <v>24.17</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3755,32 +3763,32 @@
       <c r="E40" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>85.40000000000001</v>
+      <c r="F40" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="10" t="n">
-        <v>1.8</v>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3789,7 +3797,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3801,22 +3809,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>826.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3851,26 +3859,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3879,7 +3887,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3897,7 +3905,7 @@
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3924,25 +3932,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="K42" s="3" t="n">
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3950,26 +3958,26 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" s="10" t="n">
-        <v>82</v>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V42" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V42" s="11" t="n">
         <v>2.2</v>
       </c>
-      <c r="W42" s="10" t="n">
-        <v>0.7</v>
+      <c r="W42" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -3997,7 +4005,7 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="13" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="13" t="inlineStr"/>
       <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
@@ -4036,7 +4044,7 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="13" t="inlineStr"/>
       <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
@@ -4066,13 +4074,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="10" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="E45" s="10" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F45" s="10" t="n">
         <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4085,50 +4093,50 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>111.9</v>
+        <v>7.7</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>11.2</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="R45" s="9" t="n">
+      <c r="Q45" s="10" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="R45" s="10" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>241.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>892.7</v>
-      </c>
-      <c r="W45" s="9" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="W45" s="10" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>232.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>8.199999999999999</v>
@@ -4147,14 +4155,14 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>1.8</v>
+      <c r="F46" s="10" t="n">
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4163,56 +4171,56 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q46" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L46" s="9" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="M46" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q46" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="10" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V46" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V46" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>2.4</v>
+      <c r="W46" s="10" t="n">
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -165,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,10 +772,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -805,40 +796,40 @@
       <c r="K4" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.1</v>
+        <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="9" t="n">
-        <v>23.8</v>
+      <c r="R4" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>4.5</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -858,14 +849,14 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
@@ -882,14 +873,14 @@
       <c r="K5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>20.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -897,25 +888,25 @@
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -941,14 +932,14 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.2</v>
@@ -963,16 +954,16 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -980,10 +971,10 @@
       <c r="P6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -995,17 +986,17 @@
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1024,10 +1015,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
@@ -1048,10 +1039,10 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1063,14 +1054,14 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1078,10 +1069,10 @@
       <c r="U7" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1107,13 +1098,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>42.6</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1131,23 +1122,23 @@
       <c r="K8" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1159,10 +1150,10 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1188,13 +1179,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>147.4</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -1207,15 +1198,15 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K9" s="9" t="n">
         <v>44.1</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1227,10 +1218,10 @@
       <c r="P9" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="9" t="n">
         <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1242,11 +1233,11 @@
       <c r="U9" s="3" t="n">
         <v>48.8</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="10" t="n">
-        <v>10.8</v>
+      <c r="W9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1271,20 +1262,20 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
@@ -1295,22 +1286,22 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>9.1</v>
+        <v>291.3</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="R10" s="9" t="n">
@@ -1320,15 +1311,15 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1354,10 +1345,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="F11" s="3" t="n">
@@ -1368,7 +1359,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1387,10 +1378,10 @@
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1405,7 +1396,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1431,17 +1422,17 @@
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.1</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
@@ -1462,7 +1453,7 @@
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
@@ -1470,10 +1461,10 @@
       <c r="P12" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1488,7 +1479,7 @@
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1514,11 +1505,11 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>18.5</v>
+      <c r="E13" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
@@ -1545,7 +1536,7 @@
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1553,17 +1544,17 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>84.2</v>
+        <v>74.2</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1571,14 +1562,14 @@
       <c r="V13" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>20</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1599,10 +1590,10 @@
       <c r="C14" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
@@ -1612,7 +1603,7 @@
         <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1621,7 +1612,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>22.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1630,7 +1621,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1638,17 +1629,17 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1656,14 +1647,14 @@
       <c r="V14" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>77.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>5.4</v>
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="F15" s="3" t="n">
@@ -1698,7 +1689,7 @@
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1713,7 +1704,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1721,14 +1712,14 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.7</v>
+        <v>10.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1739,17 +1730,17 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1765,48 +1756,48 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>140.4</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>116.5</v>
+      <c r="F16" s="9" t="n">
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
+      <c r="L16" s="9" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="9" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>53.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>122.2</v>
+      <c r="Q16" s="8" t="n">
+        <v>129.2</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>112.5</v>
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1815,19 +1806,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>114</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>10.2</v>
+        <v>41.2</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>10.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1846,15 +1837,15 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1867,17 +1858,17 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>18.8</v>
+      <c r="L17" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1885,11 +1876,11 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>25.3</v>
@@ -1900,14 +1891,14 @@
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="V17" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1942,7 +1933,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1950,17 +1941,17 @@
       <c r="J18" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="11" t="n">
-        <v>1.1</v>
+      <c r="M18" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91.2</v>
@@ -1968,10 +1959,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="10" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1981,10 +1972,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>21.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="V18" s="10" t="n">
+        <v>12.18</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2012,7 +2003,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>30.5</v>
@@ -2035,17 +2026,17 @@
       <c r="J19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2056,7 +2047,7 @@
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2068,7 +2059,7 @@
       <c r="U19" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2078,7 +2069,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>87.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2097,7 +2088,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.5</v>
@@ -2109,7 +2100,7 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9</v>
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2118,15 +2109,15 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2136,29 +2127,29 @@
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V20" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>85.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2183,7 +2174,7 @@
         <v>1.1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.3</v>
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2203,13 +2194,13 @@
       <c r="J21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2224,26 +2215,26 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>12.1</v>
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>28.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>90.2</v>
@@ -2265,7 +2256,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>29.4</v>
@@ -2288,17 +2279,17 @@
       <c r="J22" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2309,7 +2300,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2319,9 +2310,9 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="V22" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2350,14 +2341,14 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="10" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
+      <c r="D23" s="9" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>12.2</v>
+      <c r="F23" s="9" t="n">
+        <v>112.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.2</v>
@@ -2371,48 +2362,48 @@
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="10" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L23" s="10" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="M23" s="10" t="n">
+      <c r="K23" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="M23" s="9" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="R23" s="8" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="V23" s="10" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V23" s="9" t="n">
         <v>108.4</v>
       </c>
-      <c r="W23" s="10" t="n">
+      <c r="W23" s="9" t="n">
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>27.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2433,13 +2424,13 @@
       <c r="C24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2449,18 +2440,18 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>991999.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2472,11 +2463,11 @@
       <c r="P24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="10" t="n">
-        <v>2.4</v>
+      <c r="R24" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
@@ -2490,7 +2481,7 @@
       <c r="V24" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2500,7 +2491,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2516,14 +2507,14 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>24.3</v>
+      <c r="F25" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
@@ -2532,7 +2523,7 @@
         <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2540,7 +2531,7 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M25" s="3" t="n">
@@ -2550,15 +2541,15 @@
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="10" t="n">
         <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2573,11 +2564,11 @@
       <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="10" t="n">
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>67.2</v>
@@ -2599,23 +2590,23 @@
       <c r="C26" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E26" s="3" t="n">
+      <c r="D26" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2623,17 +2614,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2642,7 +2633,7 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>27.1</v>
@@ -2682,13 +2673,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2704,16 +2695,16 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L27" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M27" s="11" t="n">
-        <v>1.8</v>
+      <c r="M27" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>98.2</v>
@@ -2731,7 +2722,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2765,13 +2756,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F28" s="9" t="n">
+      <c r="E28" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2789,23 +2780,23 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2817,16 +2808,16 @@
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2848,13 +2839,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2872,10 +2863,10 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M29" s="13" t="inlineStr"/>
+      <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
         <v>9.6</v>
       </c>
@@ -2892,7 +2883,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>72.2</v>
@@ -2913,7 +2904,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2932,11 +2923,11 @@
       <c r="D30" s="9" t="n">
         <v>148.4</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>118.1</v>
+      <c r="F30" s="8" t="n">
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2950,41 +2941,41 @@
       <c r="J30" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="M30" s="10" t="n">
-        <v>9.199999999999999</v>
+      <c r="M30" s="9" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>130.7</v>
       </c>
-      <c r="R30" s="10" t="n">
-        <v>12.9</v>
+      <c r="R30" s="9" t="n">
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W30" s="10" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W30" s="9" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3013,11 +3004,11 @@
       <c r="D31" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
@@ -3033,13 +3024,13 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>2.8</v>
+        <v>24</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3047,10 +3038,10 @@
       <c r="P31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3062,10 +3053,10 @@
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V31" s="10" t="n">
+      <c r="V31" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3093,47 +3084,47 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E32" s="11" t="n">
+      <c r="D32" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>4.5</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="10" t="n">
         <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="13" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3145,10 +3136,10 @@
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="9" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W32" s="9" t="n">
+      <c r="V32" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3174,14 +3165,14 @@
       <c r="C33" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="8" t="n">
         <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>94.59999999999999</v>
@@ -3195,45 +3186,45 @@
       <c r="J33" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M33" s="10" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>9</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>27.8</v>
+      <c r="R33" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>78.2</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V33" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>2.8</v>
@@ -3255,9 +3246,9 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
@@ -3278,17 +3269,17 @@
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="11" t="n">
+      <c r="M34" s="10" t="n">
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>87.2</v>
@@ -3296,10 +3287,10 @@
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3309,12 +3300,12 @@
         <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V34" s="9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3342,14 +3333,14 @@
       <c r="C35" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="8" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>24.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
@@ -3363,17 +3354,17 @@
       <c r="J35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="11" t="n">
-        <v>1.8</v>
+      <c r="M35" s="10" t="n">
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>92.2</v>
@@ -3381,25 +3372,25 @@
       <c r="P35" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="V35" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3409,7 +3400,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.2</v>
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3425,8 +3416,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="11" t="n">
-        <v>93.59999999999999</v>
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3435,7 +3426,7 @@
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3446,17 +3437,17 @@
       <c r="J36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M36" s="11" t="n">
-        <v>1.8</v>
+      <c r="M36" s="10" t="n">
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
@@ -3464,25 +3455,25 @@
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.4</v>
+        <v>44.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3508,13 +3499,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="8" t="n">
         <v>161.5</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3529,32 +3520,32 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>49.1</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="9" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="M37" s="10" t="n">
-        <v>2.1</v>
+      <c r="M37" s="9" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>50.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="10" t="n">
-        <v>17.5</v>
+      <c r="R37" s="8" t="n">
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3562,10 +3553,10 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="10" t="n">
-        <v>111</v>
-      </c>
-      <c r="W37" s="9" t="n">
+      <c r="V37" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3575,7 +3566,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>24.7</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3591,14 +3582,14 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="10" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="D38" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>25.5</v>
+      <c r="F38" s="9" t="n">
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3613,16 +3604,16 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="L38" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="M38" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" s="9" t="n">
         <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.5</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
@@ -3630,32 +3621,32 @@
       <c r="P38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>14.1</v>
@@ -3677,7 +3668,7 @@
       <c r="D39" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="10" t="n">
         <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
@@ -3695,18 +3686,18 @@
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3718,7 +3709,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3729,14 +3720,14 @@
       <c r="V39" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W39" s="11" t="n">
-        <v>24.17</v>
+      <c r="W39" s="10" t="n">
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3778,17 +3769,17 @@
       <c r="J40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3797,7 +3788,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.2</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3809,22 +3800,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3850,7 +3841,7 @@
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3861,7 +3852,7 @@
       <c r="J41" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
@@ -3899,7 +3890,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3921,7 +3912,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
       <c r="E42" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3932,7 +3923,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3940,7 +3931,7 @@
       <c r="J42" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -3950,7 +3941,7 @@
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3968,16 +3959,16 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V42" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
+      </c>
+      <c r="V42" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -3998,26 +3989,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="13" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="13" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
-      <c r="R43" s="13" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="12" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4037,26 +4028,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="13" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
-      <c r="R44" s="13" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="13" t="inlineStr"/>
-      <c r="W44" s="13" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="12" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4074,13 +4065,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="9" t="n">
         <v>122.3</v>
       </c>
-      <c r="E45" s="10" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="F45" s="10" t="n">
+      <c r="E45" s="9" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
@@ -4095,14 +4086,14 @@
       <c r="J45" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="L45" s="10" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>11.2</v>
+      <c r="L45" s="9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
@@ -4111,35 +4102,35 @@
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="10" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="R45" s="10" t="n">
+      <c r="Q45" s="9" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="R45" s="9" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.8</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V45" s="10" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="V45" s="9" t="n">
         <v>85.7</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="9" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>232.7</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4155,13 +4146,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="9" t="n">
         <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4177,27 +4168,27 @@
         <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L46" s="10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M46" s="10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M46" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="9" t="n">
         <v>25.7</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4207,20 +4198,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="V46" s="10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="V46" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>2.2</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -806,7 +806,7 @@
         <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -814,8 +814,8 @@
       <c r="Q4" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>29.8</v>
+      <c r="R4" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
@@ -880,7 +880,7 @@
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -891,14 +891,14 @@
       <c r="Q5" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>28.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>7</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>6.5</v>
@@ -954,7 +954,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>17.4</v>
@@ -963,7 +963,7 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -974,7 +974,7 @@
       <c r="Q6" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -996,7 +996,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>37.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1049,7 +1049,7 @@
         <v>2.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
@@ -1057,11 +1057,11 @@
       <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1079,7 +1079,7 @@
         <v>24.6</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>74.2</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>23.8</v>
@@ -1120,7 +1120,7 @@
         <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>18.9</v>
@@ -1138,7 +1138,7 @@
       <c r="Q8" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1221,8 +1221,8 @@
       <c r="Q9" s="9" t="n">
         <v>129.4</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>110.1</v>
+      <c r="R9" s="8" t="n">
+        <v>110.8</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1236,14 +1236,14 @@
       <c r="V9" s="8" t="n">
         <v>123.8</v>
       </c>
-      <c r="W9" s="8" t="n">
-        <v>110.8</v>
+      <c r="W9" s="9" t="n">
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>382.6</v>
+        <v>382</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>31.1</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.2</v>
@@ -1296,7 +1296,7 @@
         <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>291.3</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1304,7 +1304,7 @@
       <c r="Q10" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>22</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1359,15 +1359,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>12.3</v>
+      <c r="M11" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1403,7 +1403,7 @@
         <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>4.5</v>
@@ -1449,20 +1449,20 @@
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1471,10 +1471,10 @@
         <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>6.7</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1486,7 +1486,7 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>83.2</v>
@@ -1530,13 +1530,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M13" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1554,7 +1554,7 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>74.2</v>
+        <v>7.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1569,7 +1569,7 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>29.9</v>
@@ -1612,12 +1612,12 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1636,7 +1636,7 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1700,14 +1700,14 @@
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
@@ -1719,7 +1719,7 @@
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>10.7</v>
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1769,32 +1769,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="9" t="n">
         <v>95.3</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>153.2</v>
+        <v>35.3</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q16" s="8" t="n">
-        <v>129.2</v>
+      <c r="Q16" s="9" t="n">
+        <v>10.9</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>182.5</v>
@@ -1809,16 +1809,16 @@
         <v>41.2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>116.7</v>
+        <v>11.4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>408.9</v>
+        <v>708.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>28.1</v>
@@ -1852,7 +1852,7 @@
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
@@ -1864,11 +1864,11 @@
       <c r="L17" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.1</v>
+        <v>0.2</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1901,7 +1901,7 @@
         <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2</v>
@@ -1936,7 +1936,7 @@
         <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1944,10 +1944,10 @@
       <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1962,7 +1962,7 @@
       <c r="Q18" s="10" t="n">
         <v>89.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1975,7 +1975,7 @@
         <v>10.1</v>
       </c>
       <c r="V18" s="10" t="n">
-        <v>12.18</v>
+        <v>1.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>30.5</v>
@@ -2029,17 +2029,17 @@
       <c r="K19" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>18.2</v>
+      <c r="L19" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.2</v>
@@ -2047,14 +2047,14 @@
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0.2</v>
@@ -2069,7 +2069,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.2</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.5</v>
@@ -2100,7 +2100,7 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.6</v>
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2109,15 +2109,15 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       <c r="Q20" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2149,7 +2149,7 @@
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>25.3</v>
+        <v>85.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2189,7 +2189,7 @@
         <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1.9</v>
@@ -2197,14 +2197,14 @@
       <c r="K21" s="8" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
@@ -2215,14 +2215,14 @@
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>28.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
@@ -2234,10 +2234,10 @@
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2256,13 +2256,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>23.2</v>
@@ -2282,14 +2282,14 @@
       <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2300,7 +2300,7 @@
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2310,7 +2310,7 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.9</v>
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24.6</v>
@@ -2319,7 +2319,7 @@
         <v>26.2</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>22.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>80.2</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="9" t="n">
-        <v>147.6</v>
+        <v>147.5</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>90.40000000000001</v>
@@ -2372,26 +2372,26 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451.2</v>
+        <v>45.7</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>107.2</v>
+      <c r="R23" s="9" t="n">
+        <v>107.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>34.7</v>
+        <v>57.7</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>108.4</v>
@@ -2400,7 +2400,7 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.8</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>427.6</v>
@@ -2446,19 +2446,19 @@
         <v>1.8</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>31.2</v>
+        <v>81.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2466,14 +2466,14 @@
       <c r="Q24" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="R24" s="8" t="n">
-        <v>21.4</v>
+      <c r="R24" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.2</v>
+        <v>78.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2491,7 +2491,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2507,14 +2507,14 @@
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
@@ -2531,17 +2531,17 @@
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92.2</v>
+        <v>0.9</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>29.6</v>
+        <v>0</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>19.2</v>
@@ -2600,13 +2600,13 @@
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2614,17 +2614,17 @@
       <c r="K26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>76.2</v>
+        <v>7.6</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2651,7 +2651,7 @@
         <v>21.3</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="E27" s="8" t="n">
@@ -2686,7 +2686,7 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2695,25 +2695,25 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2722,7 +2722,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.7</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -2780,20 +2780,20 @@
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.1</v>
@@ -2811,16 +2811,16 @@
         <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>216.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>53.2</v>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="8" t="n">
         <v>30.1</v>
       </c>
       <c r="E29" s="8" t="n">
@@ -2863,12 +2863,12 @@
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="M29" s="12" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90.59999999999999</v>
@@ -2898,7 +2898,7 @@
         <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
@@ -2920,14 +2920,14 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>148.4</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>119.1</v>
+      <c r="F30" s="9" t="n">
+        <v>11.8</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2948,11 +2948,11 @@
         <v>92.5</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2973,13 +2973,13 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>104.6</v>
+        <v>10.4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>114.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>372.2</v>
+        <v>382.8</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>32.4</v>
@@ -3001,20 +3001,20 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>22.9</v>
+      <c r="E31" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
@@ -3023,14 +3023,14 @@
         <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>18.9</v>
+      <c r="L31" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>22.6</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>32.8</v>
@@ -3108,12 +3108,12 @@
       <c r="K32" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="12" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>91.2</v>
@@ -3124,7 +3124,7 @@
       <c r="Q32" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3136,7 +3136,7 @@
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W32" s="8" t="n">
@@ -3172,10 +3172,10 @@
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3189,7 +3189,7 @@
       <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="M33" s="10" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>90.3</v>
+        <v>80.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3205,20 +3205,20 @@
       <c r="Q33" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>24.8</v>
+      <c r="R33" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>22</v>
+        <v>24.2</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>27.4</v>
@@ -3272,17 +3272,17 @@
       <c r="K34" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
@@ -3290,7 +3290,7 @@
       <c r="Q34" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3302,14 +3302,14 @@
       <c r="U34" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>86.3</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>6.7</v>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>30.4</v>
@@ -3340,10 +3340,10 @@
         <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.2</v>
@@ -3357,25 +3357,25 @@
       <c r="K35" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="10" t="n">
         <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3385,9 +3385,9 @@
         <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -3435,22 +3435,22 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3458,7 +3458,7 @@
       <c r="Q36" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3470,7 +3470,7 @@
       <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="W36" s="8" t="n">
@@ -3480,7 +3480,7 @@
         <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>17.6</v>
@@ -3503,7 +3503,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>126.9</v>
@@ -3527,13 +3527,13 @@
         <v>95.09999999999999</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.4</v>
+        <v>450</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.6</v>
@@ -3541,11 +3541,11 @@
       <c r="Q37" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="R37" s="9" t="n">
         <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>190.4</v>
+        <v>19</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3553,7 +3553,7 @@
       <c r="U37" s="3" t="n">
         <v>124.7</v>
       </c>
-      <c r="V37" s="8" t="n">
+      <c r="V37" s="9" t="n">
         <v>110</v>
       </c>
       <c r="W37" s="8" t="n">
@@ -3566,7 +3566,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.2</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>18.4</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3604,39 +3604,39 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R38" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="R38" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>49.2</v>
+        <v>4.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="V38" s="8" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="W38" s="8" t="n">
@@ -3646,10 +3646,10 @@
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3692,17 +3692,17 @@
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>32.5</v>
@@ -3775,19 +3775,19 @@
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>18.2</v>
+      <c r="M40" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>29.8</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3800,7 +3800,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3809,13 +3809,13 @@
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>82.8</v>
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3858,7 +3858,7 @@
       <c r="L41" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -3868,7 +3868,7 @@
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3878,7 +3878,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3890,7 +3890,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3923,7 +3923,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3937,11 +3937,11 @@
       <c r="L42" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3949,7 +3949,7 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="8" t="n">
         <v>25</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -3959,13 +3959,13 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="W42" s="10" t="n">
         <v>0.2</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="12" t="inlineStr"/>
@@ -3998,11 +3998,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
       <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="12" t="inlineStr"/>
@@ -4037,11 +4037,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
       <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>34.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>102</v>
@@ -4090,32 +4090,32 @@
         <v>7.7</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>14.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>11.1</v>
+        <v>31.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>266.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>106.9</v>
+      <c r="Q45" s="8" t="n">
+        <v>106.7</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>24.1</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.3</v>
+        <v>95.3</v>
       </c>
       <c r="V45" s="9" t="n">
         <v>85.7</v>
@@ -4124,13 +4124,13 @@
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>327.2</v>
+        <v>32.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>13.7</v>
@@ -4173,17 +4173,17 @@
       <c r="L46" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M46" s="9" t="n">
-        <v>19.9</v>
+      <c r="M46" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0.2</v>
@@ -4195,7 +4195,7 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>29.8</v>
@@ -4209,9 +4209,7 @@
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
         <v>298.9</v>
       </c>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,6 +165,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1179,7 +1188,7 @@
       <c r="J9" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>44.2</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1726,7 +1735,7 @@
       <c r="J16" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="11" t="n"/>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
       </c>
@@ -2275,7 +2284,7 @@
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>96.2</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2435,7 +2444,7 @@
       <c r="J25" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
@@ -2514,7 +2523,7 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
@@ -2595,7 +2604,7 @@
       <c r="J27" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
@@ -2674,7 +2683,7 @@
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
@@ -2755,7 +2764,7 @@
       <c r="J29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L29" s="3" t="n">
@@ -2836,7 +2845,7 @@
       <c r="J30" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3387,7 +3396,7 @@
       <c r="J37" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4007,7 +4016,7 @@
       <c r="J45" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>8.5</v>
       </c>
       <c r="L45" s="3" t="n">
